--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -788,7 +788,7 @@
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 6.2% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
@@ -848,7 +848,7 @@
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 6.2% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
@@ -914,37 +914,37 @@
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 86295억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 86456억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 92652억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 92811억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 98959억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 99117억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 105207억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 105365억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 105584억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 105740억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 111947억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 112101억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1808,61 +1808,61 @@
     <comment ref="AC44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 21729억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 322227억)</t>
+SLS 해양 원화 21749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 321359억)</t>
       </text>
     </comment>
     <comment ref="AD44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 21888억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 287378억)</t>
+SLS 해양 원화 21907억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억)</t>
       </text>
     </comment>
     <comment ref="AF44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 21412억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 252529억)</t>
+SLS 해양 원화 21431억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억)</t>
       </text>
     </comment>
     <comment ref="AG44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 20430억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 217680억)</t>
+SLS 해양 원화 21270억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억)</t>
       </text>
     </comment>
     <comment ref="AH44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 20443억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 182831억)</t>
+SLS 해양 원화 20443억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억)</t>
       </text>
     </comment>
     <comment ref="AI44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 19690억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 147982억)</t>
+SLS 해양 원화 19690억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억)</t>
       </text>
     </comment>
     <comment ref="AK44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 18787억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 113132억)</t>
+SLS 해양 원화 18787억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억)</t>
       </text>
     </comment>
     <comment ref="AL44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 18145억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 78283억)</t>
+SLS 해양 원화 18145억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억)</t>
       </text>
     </comment>
     <comment ref="AM44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 16812억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 43434억)</t>
+SLS 해양 원화 16812억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억)</t>
       </text>
     </comment>
     <comment ref="AN44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 15025억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 8585억)</t>
+SLS 해양 원화 15025억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억)</t>
       </text>
     </comment>
     <comment ref="AC45" authorId="0" shapeId="0">
@@ -2315,28 +2315,28 @@
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.2% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위))
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="AH9" authorId="0" shapeId="0">
+      <text>
         <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="AH9" authorId="0" shapeId="0">
+    <comment ref="AI9" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="AI9" authorId="0" shapeId="0">
+    <comment ref="AK9" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="AK9" authorId="0" shapeId="0">
-      <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위))
-[ratio]</t>
-      </text>
-    </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.2% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위))
@@ -2470,28 +2470,28 @@
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
+        <t>추정: SLS 코호트 타겟 6.2% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위)
+[yoy]</t>
+      </text>
+    </comment>
+    <comment ref="AH10" authorId="0" shapeId="0">
+      <text>
         <t>추정: SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="AH10" authorId="0" shapeId="0">
+    <comment ref="AI10" authorId="0" shapeId="0">
       <text>
         <t>추정: SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="AI10" authorId="0" shapeId="0">
+    <comment ref="AK10" authorId="0" shapeId="0">
       <text>
         <t>추정: SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
-    <comment ref="AK10" authorId="0" shapeId="0">
-      <text>
-        <t>추정: SLS 코호트 타겟 6.0% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위)
-[yoy]</t>
-      </text>
-    </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
         <t>추정: SLS 코호트 타겟 6.2% + 회사 캘리브레이션 +6.4%p(최근 4분기 실측−타겟 중위)
@@ -2536,37 +2536,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 86295억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 86456억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 92652억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 92811억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 98959억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 99117억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 105207억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 105365억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 105584억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 105740억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 111947억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 112101억 × 2.15% − 총차입금 5234억 × 4.52% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4165,61 +4165,61 @@
     </comment>
     <comment ref="AC35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21729억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 322227억)
+        <t>추정: SLS 해양 원화 21749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 321359억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21888억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 287378억)
+        <t>추정: SLS 해양 원화 21907억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21412억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 252529억)
+        <t>추정: SLS 해양 원화 21431억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20430억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 217680억)
+        <t>추정: SLS 해양 원화 21270억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20443억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 182831억)
+        <t>추정: SLS 해양 원화 20443억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19690억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 147982억)
+        <t>추정: SLS 해양 원화 19690억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18787억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 113132억)
+        <t>추정: SLS 해양 원화 18787억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18145억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 78283억)
+        <t>추정: SLS 해양 원화 18145억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 16812억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 43434억)
+        <t>추정: SLS 해양 원화 16812억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN35" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15025억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34849억(최근 4분기 '부문매출−SLS' 중위 34849억/분기, 잔여 8585억)
+        <t>추정: SLS 해양 원화 15025억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억)
 [ratio]</t>
       </text>
     </comment>
@@ -4900,7 +4900,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 24.0, "op_wape_pct": 44.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "sls_marine_plus_uncovered_backlog_runoff", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 41613.04, "rev_act": 44178.98, "op_pred": 4280.09, "op_act": 5572.85}, {"q": "2025Q4", "rev_pred": 41613.04, "rev_act": 51930.94, "op_pred": 4280.09, "op_act": 5750.35}, {"q": "2026Q1", "rev_pred": 41460.97, "rev_act": 59163.32, "op_pred": 4264.44, "op_act": 9053.86}, {"q": "2026Q2", "rev_pred": 41537.0, "rev_act": 63321.55, "op_pred": 4272.27, "op_act": 10399.38}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 24.0, "op_wape_pct": 44.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "sls_marine_plus_uncovered_backlog_runoff", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 41613.14, "rev_act": 44178.98, "op_pred": 4274.45, "op_act": 5572.85}, {"q": "2025Q4", "rev_pred": 41613.14, "rev_act": 51930.94, "op_pred": 4274.45, "op_act": 5750.35}, {"q": "2026Q1", "rev_pred": 41460.67, "rev_act": 59163.32, "op_pred": 4258.78, "op_act": 9053.86}, {"q": "2026Q2", "rev_pred": 41536.89, "rev_act": 63321.55, "op_pred": 4266.62, "op_act": 10399.38}]}</t>
         </is>
       </c>
     </row>
@@ -8821,36 +8821,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.49289</v>
+        <v>0.492887</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.273095</v>
+        <v>0.273087</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.109424</v>
+        <v>0.10941</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.021065</v>
+        <v>0.034015</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>-0.019505</v>
+        <v>-0.019802</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>-0.033237</v>
+        <v>-0.033529</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.039992</v>
+        <v>-0.04028</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.035342</v>
+        <v>-0.047724</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.056145</v>
+        <v>-0.056162</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.07299700000000001</v>
+        <v>-0.073019</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -9135,7 +9135,7 @@
         <v>0.126637</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.124137</v>
+        <v>0.125837</v>
       </c>
       <c r="AH23" s="24" t="n">
         <v>0.123937</v>
@@ -9260,7 +9260,7 @@
         <v>-0.172549</v>
       </c>
       <c r="AG24" s="24" t="n">
-        <v>-0.244214</v>
+        <v>-0.233861</v>
       </c>
       <c r="AH24" s="24" t="n">
         <v>-0.026709</v>
@@ -9273,7 +9273,7 @@
         <v>-0.022117</v>
       </c>
       <c r="AL24" s="24" t="n">
-        <v>0.01531</v>
+        <v>0.00159</v>
       </c>
       <c r="AM24" s="24" t="n">
         <v>0.046812</v>
@@ -9412,26 +9412,26 @@
         <v>401.83</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>404.1</v>
+        <v>404.96</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>438.23</v>
+        <v>439.08</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>472.09</v>
+        <v>472.94</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>505.63</v>
+        <v>506.48</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>507.66</v>
+        <v>508.5</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>541.8200000000001</v>
+        <v>542.65</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -10019,7 +10019,7 @@
         <v>0.24494</v>
       </c>
       <c r="AD29" s="24" t="n">
-        <v>0.244939</v>
+        <v>0.24494</v>
       </c>
       <c r="AE29" s="25">
         <f>IFERROR(subQ!AE16/subQ!AE15,"")</f>
@@ -10029,29 +10029,29 @@
         <v>0.24494</v>
       </c>
       <c r="AG29" s="24" t="n">
-        <v>0.24494</v>
+        <v>0.244941</v>
       </c>
       <c r="AH29" s="24" t="n">
         <v>0.24494</v>
       </c>
       <c r="AI29" s="24" t="n">
-        <v>0.24494</v>
+        <v>0.244941</v>
       </c>
       <c r="AJ29" s="25">
         <f>IFERROR(subQ!AJ16/subQ!AJ15,"")</f>
         <v/>
       </c>
       <c r="AK29" s="24" t="n">
-        <v>0.244941</v>
+        <v>0.24494</v>
       </c>
       <c r="AL29" s="24" t="n">
         <v>0.24494</v>
       </c>
       <c r="AM29" s="24" t="n">
+        <v>0.24494</v>
+      </c>
+      <c r="AN29" s="24" t="n">
         <v>0.244941</v>
-      </c>
-      <c r="AN29" s="24" t="n">
-        <v>0.24494</v>
       </c>
       <c r="AO29" s="25">
         <f>IFERROR(subQ!AO16/subQ!AO15,"")</f>
@@ -10200,10 +10200,10 @@
         <v>1</v>
       </c>
       <c r="AL30" s="24" t="n">
-        <v>1</v>
+        <v>0.9999980000000001</v>
       </c>
       <c r="AM30" s="24" t="n">
-        <v>1</v>
+        <v>0.9999980000000001</v>
       </c>
       <c r="AN30" s="24" t="n">
         <v>1</v>
@@ -10436,17 +10436,17 @@
         <v/>
       </c>
       <c r="AC32" s="29" t="n">
-        <v>0.0049</v>
+        <v>-0.0051</v>
       </c>
       <c r="AD32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>5940.24</v>
+        <v>5940.25</v>
       </c>
       <c r="AH32" s="29" t="n">
         <v>0</v>
@@ -10456,10 +10456,10 @@
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL32" s="29" t="n">
-        <v>5940.24</v>
+        <v>5940.25</v>
       </c>
       <c r="AM32" s="29" t="n">
         <v>0</v>
@@ -10564,27 +10564,27 @@
         <v/>
       </c>
       <c r="AC33" s="29" t="n">
-        <v>0.0023</v>
+        <v>-0.0077</v>
       </c>
       <c r="AD33" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AE33" s="30" t="n"/>
       <c r="AF33" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AG33" s="29" t="n">
-        <v>5940.24</v>
+        <v>5940.25</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AI33" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AL33" s="29" t="n">
         <v>5940.24</v>
@@ -10593,7 +10593,7 @@
         <v>0</v>
       </c>
       <c r="AN33" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -10823,33 +10823,33 @@
         <v>0.10999</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.09771000000000001</v>
+        <v>0.097709</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.088757</v>
+        <v>0.088756</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.005266</v>
+        <v>0.007268</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.078666</v>
+        <v>0.078495</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.072362</v>
+        <v>0.072216</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.06684900000000001</v>
+        <v>0.066723</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.003781</v>
+        <v>0.003762</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.063564</v>
+        <v>0.06345199999999999</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.058741</v>
+        <v>0.058643</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -10948,36 +10948,36 @@
         <v/>
       </c>
       <c r="AC36" s="24" t="n">
-        <v>0.100854</v>
+        <v>0.100853</v>
       </c>
       <c r="AD36" s="24" t="n">
         <v>0.090337</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.08261499999999999</v>
+        <v>0.08261400000000001</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.00493</v>
+        <v>0.006803</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07366200000000001</v>
+        <v>0.07351100000000001</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.068075</v>
+        <v>0.06794500000000001</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.063141</v>
+        <v>0.063028</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.003583</v>
+        <v>0.003566</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.060259</v>
+        <v>0.060158</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.05586</v>
+        <v>0.055772</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -11616,26 +11616,26 @@
         <v>-0.457268</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.307816</v>
+        <v>-0.311824</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>0.065204</v>
+        <v>0.058501</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>0.141564</v>
+        <v>0.134454</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>0.107874</v>
+        <v>0.101054</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>0.037058</v>
+        <v>0.043098</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>0.024027</v>
+        <v>0.030512</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.015855</v>
+        <v>0.022222</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -11735,26 +11735,26 @@
         <v>-0.416801</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>-0.413681</v>
+        <v>-0.415309</v>
       </c>
       <c r="AH43" s="24" t="n">
         <v>-0.151365</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>-0.141732</v>
+        <v>-0.144357</v>
       </c>
       <c r="AJ43" s="25" t="n"/>
       <c r="AK43" s="24" t="n">
-        <v>-0.132964</v>
+        <v>-0.135734</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>-0.133333</v>
+        <v>-0.133705</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>-0.125731</v>
+        <v>-0.128655</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>-0.122324</v>
+        <v>-0.122699</v>
       </c>
       <c r="AO43" s="25" t="n"/>
     </row>
@@ -11871,42 +11871,42 @@
         <v/>
       </c>
       <c r="AC44" s="24" t="n">
-        <v>0.857841</v>
+        <v>0.85784</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>0.858182</v>
+        <v>0.858181</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>0.857154</v>
+        <v>0.857152</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.854985</v>
+        <v>0.856801</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.855013</v>
+        <v>0.854968</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.853306</v>
+        <v>0.853261</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.851203</v>
+        <v>0.851156</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.849672</v>
+        <v>0.849624</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.846388</v>
+        <v>0.846339</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.841755</v>
+        <v>0.841702</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO5,"")</f>
@@ -12039,7 +12039,7 @@
         <v>0.126637</v>
       </c>
       <c r="AG45" s="24" t="n">
-        <v>0.124137</v>
+        <v>0.125837</v>
       </c>
       <c r="AH45" s="24" t="n">
         <v>0.123937</v>
@@ -12181,42 +12181,42 @@
         <v/>
       </c>
       <c r="AC46" s="24" t="n">
-        <v>0.142159</v>
+        <v>0.14216</v>
       </c>
       <c r="AD46" s="24" t="n">
-        <v>0.141818</v>
+        <v>0.141819</v>
       </c>
       <c r="AE46" s="25">
         <f>IFERROR(subQ!AE37/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF46" s="24" t="n">
-        <v>0.142846</v>
+        <v>0.142848</v>
       </c>
       <c r="AG46" s="24" t="n">
-        <v>0.145015</v>
+        <v>0.143199</v>
       </c>
       <c r="AH46" s="24" t="n">
-        <v>0.144987</v>
+        <v>0.145032</v>
       </c>
       <c r="AI46" s="24" t="n">
-        <v>0.146694</v>
+        <v>0.146739</v>
       </c>
       <c r="AJ46" s="25">
         <f>IFERROR(subQ!AJ37/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK46" s="24" t="n">
-        <v>0.148797</v>
+        <v>0.148843</v>
       </c>
       <c r="AL46" s="24" t="n">
-        <v>0.150328</v>
+        <v>0.150376</v>
       </c>
       <c r="AM46" s="24" t="n">
-        <v>0.153612</v>
+        <v>0.153661</v>
       </c>
       <c r="AN46" s="24" t="n">
-        <v>0.158245</v>
+        <v>0.158298</v>
       </c>
       <c r="AO46" s="25">
         <f>IFERROR(subQ!AO37/subQ!AO5,"")</f>
@@ -12349,7 +12349,7 @@
         <v>0.126637</v>
       </c>
       <c r="AG47" s="24" t="n">
-        <v>0.124137</v>
+        <v>0.125837</v>
       </c>
       <c r="AH47" s="24" t="n">
         <v>0.123937</v>
@@ -38195,52 +38195,52 @@
         </is>
       </c>
       <c r="E5" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>106.816</v>
+        <v>108.252</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>124.281</v>
+        <v>125.717</v>
       </c>
       <c r="I5" s="26" t="n">
-        <v>128.711</v>
+        <v>130.163</v>
       </c>
       <c r="J5" s="26" t="n">
-        <v>151.155</v>
+        <v>152.607</v>
       </c>
       <c r="K5" s="26" t="n">
-        <v>289.244</v>
+        <v>290.665</v>
       </c>
       <c r="L5" s="26" t="n">
-        <v>378.996</v>
+        <v>380.432</v>
       </c>
       <c r="M5" s="26" t="n">
-        <v>534.1180000000001</v>
+        <v>535.5700000000001</v>
       </c>
       <c r="N5" s="26" t="n">
-        <v>638.164</v>
+        <v>639.616</v>
       </c>
       <c r="O5" s="26" t="n">
-        <v>885.264</v>
+        <v>886.684</v>
       </c>
       <c r="P5" s="26" t="n">
-        <v>1285.208</v>
+        <v>1286.644</v>
       </c>
       <c r="Q5" s="26" t="n">
-        <v>1558.259</v>
+        <v>1559.711</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>1608.198</v>
+        <v>1609.65</v>
       </c>
       <c r="S5" s="26" t="n">
-        <v>1573.237</v>
+        <v>1574.658</v>
       </c>
       <c r="T5" s="26" t="n">
-        <v>1498.802</v>
+        <v>1562.079</v>
       </c>
       <c r="U5" s="26" t="n">
         <v>1499.739</v>
@@ -38321,19 +38321,19 @@
         <v>8.81</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>187.916</v>
+        <v>190.82</v>
       </c>
       <c r="AV5" s="26" t="n">
-        <v>510.963</v>
+        <v>516.739</v>
       </c>
       <c r="AW5" s="26" t="n">
-        <v>1840.522</v>
+        <v>1846.283</v>
       </c>
       <c r="AX5" s="26" t="n">
-        <v>5336.929</v>
+        <v>5342.689</v>
       </c>
       <c r="AY5" s="26" t="n">
-        <v>6017.062</v>
+        <v>6081.76</v>
       </c>
       <c r="AZ5" s="26" t="n">
         <v>5069.485</v>
@@ -38366,67 +38366,67 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>92.937</v>
+        <v>94.373</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>92.937</v>
+        <v>94.373</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="J6" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="K6" s="26" t="n">
-        <v>91.91500000000001</v>
+        <v>93.336</v>
       </c>
       <c r="L6" s="26" t="n">
-        <v>92.937</v>
+        <v>94.373</v>
       </c>
       <c r="M6" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="O6" s="26" t="n">
-        <v>91.91500000000001</v>
+        <v>93.336</v>
       </c>
       <c r="P6" s="26" t="n">
-        <v>92.937</v>
+        <v>94.373</v>
       </c>
       <c r="Q6" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>91.91500000000001</v>
+        <v>93.336</v>
       </c>
       <c r="T6" s="26" t="n">
-        <v>1.021</v>
+        <v>64.298</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>187.916</v>
+        <v>190.82</v>
       </c>
       <c r="AV6" s="26" t="n">
-        <v>373.79</v>
+        <v>379.566</v>
       </c>
       <c r="AW6" s="26" t="n">
-        <v>372.768</v>
+        <v>378.529</v>
       </c>
       <c r="AX6" s="26" t="n">
-        <v>372.768</v>
+        <v>378.529</v>
       </c>
       <c r="AY6" s="26" t="n">
-        <v>92.93600000000001</v>
+        <v>157.634</v>
       </c>
     </row>
     <row r="7">
@@ -39179,52 +39179,52 @@
         </is>
       </c>
       <c r="E15" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="G15" s="26" t="n">
-        <v>92.937</v>
+        <v>94.373</v>
       </c>
       <c r="H15" s="26" t="n">
-        <v>92.937</v>
+        <v>94.373</v>
       </c>
       <c r="I15" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="J15" s="26" t="n">
-        <v>93.958</v>
+        <v>95.41</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>214.692</v>
+        <v>216.112</v>
       </c>
       <c r="L15" s="26" t="n">
-        <v>290.41</v>
+        <v>291.846</v>
       </c>
       <c r="M15" s="26" t="n">
-        <v>410.187</v>
+        <v>411.639</v>
       </c>
       <c r="N15" s="26" t="n">
-        <v>437.173</v>
+        <v>438.625</v>
       </c>
       <c r="O15" s="26" t="n">
-        <v>485.198</v>
+        <v>486.618</v>
       </c>
       <c r="P15" s="26" t="n">
-        <v>567.905</v>
+        <v>569.341</v>
       </c>
       <c r="Q15" s="26" t="n">
-        <v>642.463</v>
+        <v>643.915</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>642.463</v>
+        <v>643.915</v>
       </c>
       <c r="S15" s="26" t="n">
-        <v>628.496</v>
+        <v>629.917</v>
       </c>
       <c r="T15" s="26" t="n">
-        <v>543.564</v>
+        <v>606.841</v>
       </c>
       <c r="U15" s="26" t="n">
         <v>539.274</v>
@@ -39257,19 +39257,19 @@
         <v>32.427</v>
       </c>
       <c r="AU15" s="26" t="n">
-        <v>187.916</v>
+        <v>190.82</v>
       </c>
       <c r="AV15" s="26" t="n">
-        <v>373.79</v>
+        <v>379.566</v>
       </c>
       <c r="AW15" s="26" t="n">
-        <v>1352.462</v>
+        <v>1358.222</v>
       </c>
       <c r="AX15" s="26" t="n">
-        <v>2338.029</v>
+        <v>2343.789</v>
       </c>
       <c r="AY15" s="26" t="n">
-        <v>2221.502</v>
+        <v>2286.2</v>
       </c>
       <c r="AZ15" s="26" t="n">
         <v>1905.667</v>
@@ -39806,46 +39806,46 @@
         <v>1315.69</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>1317.57</v>
+        <v>1317.54</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>1325.95</v>
+        <v>1325.84</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>1327.33</v>
+        <v>1327.2</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>1337.57</v>
+        <v>1337.36</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>1391.43</v>
+        <v>1391.06</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>1400.28</v>
+        <v>1399.96</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>1399.04</v>
+        <v>1398.81</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>1404.94</v>
+        <v>1404.74</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>1420.74</v>
+        <v>1420.57</v>
       </c>
       <c r="P20" s="13" t="n">
-        <v>1441.85</v>
+        <v>1441.71</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>1448.4</v>
+        <v>1448.28</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>1447.51</v>
+        <v>1447.39</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>1447.51</v>
+        <v>1447.39</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1455.59</v>
+        <v>1449.93</v>
       </c>
       <c r="U20" s="13" t="n">
         <v>1456.48</v>
@@ -40082,46 +40082,46 @@
         <v>1317.59</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>1321.34</v>
+        <v>1321.32</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>1339.55</v>
+        <v>1339.47</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>1336</v>
+        <v>1335.9</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>1355.19</v>
+        <v>1355.04</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>1409.69</v>
+        <v>1409.43</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>1399.75</v>
+        <v>1399.53</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>1395.41</v>
+        <v>1395.25</v>
       </c>
       <c r="N22" s="13" t="n">
-        <v>1418.22</v>
+        <v>1418.08</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>1434.35</v>
+        <v>1434.24</v>
       </c>
       <c r="P22" s="13" t="n">
-        <v>1459.82</v>
+        <v>1459.72</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>1439.8</v>
+        <v>1439.71</v>
       </c>
       <c r="R22" s="13" t="n">
-        <v>1419.26</v>
+        <v>1419.18</v>
       </c>
       <c r="S22" s="13" t="n">
-        <v>1419.26</v>
+        <v>1419.18</v>
       </c>
       <c r="T22" s="13" t="n">
-        <v>1424.92</v>
+        <v>1420.96</v>
       </c>
       <c r="U22" s="13" t="n">
         <v>1425.55</v>
@@ -40214,52 +40214,52 @@
         </is>
       </c>
       <c r="E23" s="18" t="n">
-        <v>123561.2</v>
+        <v>125470.6</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>123797.7</v>
+        <v>125710.8</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>141139.8</v>
+        <v>143035.6</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>166480.8</v>
+        <v>168394.3</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>171957.4</v>
+        <v>173885.4</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>204843.7</v>
+        <v>206789.1</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>407743.8</v>
+        <v>409670.8</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>530501.2</v>
+        <v>532426.4</v>
       </c>
       <c r="M23" s="18" t="n">
-        <v>745314.7</v>
+        <v>747256</v>
       </c>
       <c r="N23" s="18" t="n">
-        <v>905055.3</v>
+        <v>907023.7</v>
       </c>
       <c r="O23" s="18" t="n">
-        <v>1269782.9</v>
+        <v>1271715.7</v>
       </c>
       <c r="P23" s="18" t="n">
-        <v>1876170.7</v>
+        <v>1878140.4</v>
       </c>
       <c r="Q23" s="18" t="n">
-        <v>2243575.6</v>
+        <v>2245531.2</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>2282458.9</v>
+        <v>2284385.7</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>2232840.3</v>
+        <v>2234725.1</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>2135678.7</v>
+        <v>2219646.3</v>
       </c>
       <c r="U23" s="18" t="n">
         <v>2137945.4</v>
@@ -40340,19 +40340,19 @@
         <v>12513.4</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>247358.9</v>
+        <v>251181.4</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>684421.7</v>
+        <v>692104.4</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>2588615</v>
+        <v>2596376.9</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>7671988.1</v>
+        <v>7679773</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>8569180.1</v>
+        <v>8655032.5</v>
       </c>
       <c r="AZ23" s="18" t="n">
         <v>7249554.8</v>
@@ -40391,28 +40391,28 @@
         <v>0.1</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>0.0935</v>
+        <v>0.0936</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0814</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>0.0793</v>
+        <v>0.0795</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>0.0708</v>
+        <v>0.0711</v>
       </c>
       <c r="K24" s="21" t="n">
-        <v>0.0815</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="L24" s="21" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="M24" s="21" t="n">
         <v>0.08210000000000001</v>
       </c>
       <c r="N24" s="21" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="O24" s="21" t="n">
         <v>0.0688</v>
@@ -40430,7 +40430,7 @@
         <v>0.0625</v>
       </c>
       <c r="T24" s="21" t="n">
-        <v>0.06</v>
+        <v>0.0617</v>
       </c>
       <c r="U24" s="21" t="n">
         <v>0.0598</v>
@@ -40605,96 +40605,96 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20241223800052</t>
+          <t>20250123800036</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OFFSH</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3716000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2558.735</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1452.28</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2028-12-29</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>④호황</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="L29" t="b">
         <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1842200</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1400.178</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1315.69</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2023-07-01</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2027-04-01</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>④호황</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="L29" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20250123800036</t>
+          <t>20250213800540</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>NAVAL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>3716000</v>
+        <v>714100</v>
       </c>
       <c r="E30" t="n">
-        <v>2558.735</v>
+        <v>516.08</v>
       </c>
       <c r="F30" t="n">
-        <v>1452.28</v>
+        <v>1383.7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2028-12-29</t>
+          <t>2031-04-13</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -40709,44 +40709,44 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20250213800540</t>
+          <t>20250304800166</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NAVAL</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>714100</v>
+        <v>458800</v>
       </c>
       <c r="E31" t="n">
-        <v>516.08</v>
+        <v>315.917</v>
       </c>
       <c r="F31" t="n">
-        <v>1383.7</v>
+        <v>1452.28</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2031-04-13</t>
+          <t>2028-12-31</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -40761,7 +40761,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20250304800166</t>
+          <t>20250422800296</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -40773,27 +40773,27 @@
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>458800</v>
+        <v>310100</v>
       </c>
       <c r="E32" t="n">
-        <v>315.917</v>
+        <v>233.133</v>
       </c>
       <c r="F32" t="n">
-        <v>1452.28</v>
+        <v>1330.14</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2028-12-31</t>
+          <t>2027-08-31</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -40807,50 +40807,50 @@
         </is>
       </c>
       <c r="L32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20250422800296</t>
+          <t>20250521800001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>310100</v>
+        <v>237400</v>
       </c>
       <c r="E33" t="n">
-        <v>233.133</v>
+        <v>170.021</v>
       </c>
       <c r="F33" t="n">
-        <v>1330.14</v>
+        <v>1396.3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -40865,44 +40865,44 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20250521800001</t>
+          <t>20250610800109</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>237400</v>
+        <v>2400000</v>
       </c>
       <c r="E34" t="n">
-        <v>170.021</v>
+        <v>1716.1</v>
       </c>
       <c r="F34" t="n">
-        <v>1396.3</v>
+        <v>1398.52</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2027-09-30</t>
+          <t>2028-11-30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -40911,45 +40911,45 @@
         </is>
       </c>
       <c r="L34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20250610800109</t>
+          <t>20250613800119</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>2400000</v>
+        <v>349000</v>
       </c>
       <c r="E35" t="n">
-        <v>1716.1</v>
+        <v>249.55</v>
       </c>
       <c r="F35" t="n">
         <v>1398.52</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2028-11-30</t>
+          <t>2027-08-31</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -40963,50 +40963,50 @@
         </is>
       </c>
       <c r="L35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20250613800119</t>
+          <t>20250708800090</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>349000</v>
+        <v>417400</v>
       </c>
       <c r="E36" t="n">
-        <v>249.55</v>
+        <v>300.948</v>
       </c>
       <c r="F36" t="n">
-        <v>1398.52</v>
+        <v>1386.95</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2027-08-31</t>
+          <t>2028-03-31</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -41021,7 +41021,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20250708800090</t>
+          <t>20250908800058</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -41033,27 +41033,27 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>417400</v>
+        <v>409500</v>
       </c>
       <c r="E37" t="n">
-        <v>300.948</v>
+        <v>295.252</v>
       </c>
       <c r="F37" t="n">
         <v>1386.95</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2028-03-31</t>
+          <t>2028-02-28</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -41067,50 +41067,50 @@
         </is>
       </c>
       <c r="L37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20250908800058</t>
+          <t>20251020800152</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>409500</v>
+        <v>363300</v>
       </c>
       <c r="E38" t="n">
-        <v>295.252</v>
+        <v>250.692</v>
       </c>
       <c r="F38" t="n">
-        <v>1386.95</v>
+        <v>1449.19</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2028-02-28</t>
+          <t>2027-11-30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -41119,50 +41119,42 @@
         </is>
       </c>
       <c r="L38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20251020800152</t>
+          <t>20251030800164</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VLCC</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
+          <t>NAVAL</t>
+        </is>
       </c>
       <c r="D39" t="n">
-        <v>363300</v>
+        <v>468900</v>
       </c>
       <c r="E39" t="n">
-        <v>250.692</v>
+        <v>323.56</v>
       </c>
       <c r="F39" t="n">
         <v>1449.19</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2027-11-30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>④호황</t>
+          <t>2033-12-20</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -41177,36 +41169,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20251030800164</t>
+          <t>20251110800036</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NAVAL</t>
-        </is>
+          <t>CONT</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>468900</v>
+        <v>435300</v>
       </c>
       <c r="E40" t="n">
-        <v>323.56</v>
+        <v>300.375</v>
       </c>
       <c r="F40" t="n">
         <v>1449.19</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2033-12-20</t>
+          <t>2028-10-31</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -41215,40 +41215,40 @@
         </is>
       </c>
       <c r="L40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20251110800036</t>
+          <t>20251114800376</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>435300</v>
+        <v>256200</v>
       </c>
       <c r="E41" t="n">
-        <v>300.375</v>
+        <v>176.788</v>
       </c>
       <c r="F41" t="n">
         <v>1449.19</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -41258,7 +41258,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -41273,39 +41273,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20251114800376</t>
+          <t>20251124800125</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>256200</v>
+        <v>534600</v>
       </c>
       <c r="E42" t="n">
-        <v>176.788</v>
+        <v>368.896</v>
       </c>
       <c r="F42" t="n">
         <v>1449.19</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2028-10-31</t>
+          <t>2028-07-14</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -41319,50 +41319,50 @@
         </is>
       </c>
       <c r="L42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20251124800125</t>
+          <t>20251211800371</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>534600</v>
+        <v>354200</v>
       </c>
       <c r="E43" t="n">
-        <v>368.896</v>
+        <v>244.412</v>
       </c>
       <c r="F43" t="n">
         <v>1449.19</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2028-07-14</t>
+          <t>2028-07-31</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -41377,34 +41377,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20251211800371</t>
+          <t>20251224800145</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>354200</v>
+        <v>375000</v>
       </c>
       <c r="E44" t="n">
-        <v>244.412</v>
+        <v>258.765</v>
       </c>
       <c r="F44" t="n">
         <v>1449.19</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -41414,7 +41414,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -41423,50 +41423,50 @@
         </is>
       </c>
       <c r="L44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20251224800145</t>
+          <t>20251226800842</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>NAVAL</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>375000</v>
+        <v>844700</v>
       </c>
       <c r="E45" t="n">
-        <v>258.765</v>
+        <v>582.877</v>
       </c>
       <c r="F45" t="n">
         <v>1449.19</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2028-07-31</t>
+          <t>2029-12-20</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -41475,50 +41475,50 @@
         </is>
       </c>
       <c r="L45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20251226800842</t>
+          <t>20260106800134</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NAVAL</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>844700</v>
+        <v>1499300</v>
       </c>
       <c r="E46" t="n">
-        <v>582.877</v>
+        <v>1022.631</v>
       </c>
       <c r="F46" t="n">
-        <v>1449.19</v>
+        <v>1466.12</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2029-12-20</t>
+          <t>2029-03-27</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -41527,50 +41527,50 @@
         </is>
       </c>
       <c r="L46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260106800134</t>
+          <t>20260120800200</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>1499300</v>
+        <v>481600</v>
       </c>
       <c r="E47" t="n">
-        <v>1022.631</v>
+        <v>328.486</v>
       </c>
       <c r="F47" t="n">
         <v>1466.12</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2029-03-27</t>
+          <t>2029-06-30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -41585,44 +41585,44 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260120800200</t>
+          <t>20260226800192</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>481600</v>
+        <v>367800</v>
       </c>
       <c r="E48" t="n">
-        <v>328.486</v>
+        <v>250.866</v>
       </c>
       <c r="F48" t="n">
         <v>1466.12</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2029-06-30</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -41637,44 +41637,44 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260226800192</t>
+          <t>20260227800223</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>367800</v>
+        <v>372400</v>
       </c>
       <c r="E49" t="n">
-        <v>250.866</v>
+        <v>254.004</v>
       </c>
       <c r="F49" t="n">
         <v>1466.12</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
+          <t>2028-06-30</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -41689,44 +41689,44 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260227800223</t>
+          <t>20260305800836</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>372400</v>
+        <v>1487200</v>
       </c>
       <c r="E50" t="n">
-        <v>254.004</v>
+        <v>1014.378</v>
       </c>
       <c r="F50" t="n">
         <v>1466.12</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
+          <t>2029-11-30</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -41741,44 +41741,44 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260305800836</t>
+          <t>20260316800220</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>1487200</v>
+        <v>823700</v>
       </c>
       <c r="E51" t="n">
-        <v>1014.378</v>
+        <v>561.823</v>
       </c>
       <c r="F51" t="n">
         <v>1466.12</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2029-11-30</t>
+          <t>2028-12-31</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -41793,44 +41793,44 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260316800220</t>
+          <t>20260403800571</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>823700</v>
+        <v>611700</v>
       </c>
       <c r="E52" t="n">
-        <v>561.823</v>
+        <v>407.325</v>
       </c>
       <c r="F52" t="n">
-        <v>1466.12</v>
+        <v>1501.75</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2028-12-31</t>
+          <t>2029-05-31</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -41845,22 +41845,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260403800571</t>
+          <t>20260403800577</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>611700</v>
+        <v>239300</v>
       </c>
       <c r="E53" t="n">
-        <v>407.325</v>
+        <v>159.347</v>
       </c>
       <c r="F53" t="n">
         <v>1501.75</v>
@@ -41877,12 +41877,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2029-05-31</t>
+          <t>2028-06-30</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -41897,7 +41897,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260403800577</t>
+          <t>20260417800177</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -41906,35 +41906,35 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>239300</v>
+        <v>674700</v>
       </c>
       <c r="E54" t="n">
-        <v>159.347</v>
+        <v>449.276</v>
       </c>
       <c r="F54" t="n">
         <v>1501.75</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
+          <t>2029-11-30</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -41949,44 +41949,44 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260417800177</t>
+          <t>20260422800038</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>NAVAL</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>674700</v>
+        <v>514800</v>
       </c>
       <c r="E55" t="n">
-        <v>449.276</v>
+        <v>342.8</v>
       </c>
       <c r="F55" t="n">
         <v>1501.75</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2029-11-30</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -41995,28 +41995,25 @@
         </is>
       </c>
       <c r="L55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260422800038</t>
+          <t>20260422800175</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NAVAL</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D56" t="n">
-        <v>514800</v>
+        <v>627100</v>
       </c>
       <c r="E56" t="n">
-        <v>342.8</v>
+        <v>417.579</v>
       </c>
       <c r="F56" t="n">
         <v>1501.75</v>
@@ -42033,12 +42030,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>④호황</t>
+          <t>2030-10-21</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -42053,36 +42045,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260422800175</t>
+          <t>20260504800297</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>627100</v>
+        <v>504800</v>
       </c>
       <c r="E57" t="n">
-        <v>417.579</v>
+        <v>336.141</v>
       </c>
       <c r="F57" t="n">
         <v>1501.75</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2030-10-21</t>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -42097,44 +42097,44 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260504800297</t>
+          <t>20260508800180</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>504800</v>
+        <v>1778700</v>
       </c>
       <c r="E58" t="n">
-        <v>336.141</v>
+        <v>1184.418</v>
       </c>
       <c r="F58" t="n">
         <v>1501.75</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2029-09-30</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -42143,28 +42143,28 @@
         </is>
       </c>
       <c r="L58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260508800180</t>
+          <t>20260508800181</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>1778700</v>
+        <v>352100</v>
       </c>
       <c r="E59" t="n">
-        <v>1184.418</v>
+        <v>234.46</v>
       </c>
       <c r="F59" t="n">
         <v>1501.75</v>
@@ -42181,12 +42181,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
+          <t>2029-03-30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -42201,34 +42201,34 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260508800181</t>
+          <t>20260514800315</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>352100</v>
+        <v>743900</v>
       </c>
       <c r="E60" t="n">
-        <v>234.46</v>
+        <v>495.355</v>
       </c>
       <c r="F60" t="n">
         <v>1501.75</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -42253,39 +42253,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260514800315</t>
+          <t>20260601800384</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>VLGC</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
-        <v>743900</v>
+        <v>1416100</v>
       </c>
       <c r="E61" t="n">
-        <v>495.355</v>
+        <v>942.967</v>
       </c>
       <c r="F61" t="n">
         <v>1501.75</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2029-03-30</t>
+          <t>2030-06-30</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -42305,7 +42305,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260601800384</t>
+          <t>20260608800378</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -42314,30 +42314,30 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>1416100</v>
+        <v>360700</v>
       </c>
       <c r="E62" t="n">
-        <v>942.967</v>
+        <v>240.186</v>
       </c>
       <c r="F62" t="n">
         <v>1501.75</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2030-06-30</t>
+          <t>2029-11-30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -42351,50 +42351,50 @@
         </is>
       </c>
       <c r="L62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260608800378</t>
+          <t>20260701800212</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>LNGC</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>360700</v>
+        <v>492800</v>
       </c>
       <c r="E63" t="n">
-        <v>240.186</v>
+        <v>328.15</v>
       </c>
       <c r="F63" t="n">
         <v>1501.75</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2029-11-30</t>
+          <t>2029-05-31</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -42409,7 +42409,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260701800212</t>
+          <t>20260701800215</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -42421,10 +42421,10 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>492800</v>
+        <v>392200</v>
       </c>
       <c r="E64" t="n">
-        <v>328.15</v>
+        <v>261.162</v>
       </c>
       <c r="F64" t="n">
         <v>1501.75</v>
@@ -42441,12 +42441,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2029-05-31</t>
+          <t>2029-01-31</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -42455,45 +42455,45 @@
         </is>
       </c>
       <c r="L64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260701800215</t>
+          <t>20260709800137</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LNGC</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>392200</v>
+        <v>469900</v>
       </c>
       <c r="E65" t="n">
-        <v>261.162</v>
+        <v>330.981</v>
       </c>
       <c r="F65" t="n">
-        <v>1501.75</v>
+        <v>1419.72</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2029-01-31</t>
+          <t>2029-06-30</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -42513,39 +42513,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260709800137</t>
+          <t>20260714800534</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>PCTC</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>469900</v>
+        <v>398500</v>
       </c>
       <c r="E66" t="n">
-        <v>330.981</v>
+        <v>265.357</v>
       </c>
       <c r="F66" t="n">
-        <v>1419.72</v>
+        <v>1501.75</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2029-06-30</t>
+          <t>2028-11-30</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -42565,44 +42565,36 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260714800534</t>
+          <t>20260810800144</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PCTC</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>2</v>
+          <t>OTHER</t>
+        </is>
       </c>
       <c r="D67" t="n">
-        <v>398500</v>
+        <v>956000</v>
       </c>
       <c r="E67" t="n">
-        <v>265.357</v>
+        <v>673.372</v>
       </c>
       <c r="F67" t="n">
-        <v>1501.75</v>
+        <v>1419.72</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2028-11-30</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>③중마진</t>
+          <t>2030-07-30</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -42611,42 +42603,50 @@
         </is>
       </c>
       <c r="L67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260810800144</t>
+          <t>20260824800122</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>956000</v>
+        <v>515400</v>
       </c>
       <c r="E68" t="n">
-        <v>673.372</v>
+        <v>363.029</v>
       </c>
       <c r="F68" t="n">
         <v>1419.72</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2030-07-30</t>
+          <t>2030-03-31</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>②BEP</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -42655,50 +42655,50 @@
         </is>
       </c>
       <c r="L68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260824800122</t>
+          <t>20260922800219</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VLGC</t>
+          <t>PCTC</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>515400</v>
+        <v>336200</v>
       </c>
       <c r="E69" t="n">
-        <v>363.029</v>
+        <v>236.807</v>
       </c>
       <c r="F69" t="n">
         <v>1419.72</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2030-03-31</t>
+          <t>2029-11-30</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -42713,44 +42713,44 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260922800219</t>
+          <t>20260930800154</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PCTC</t>
+          <t>OFFSH</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>336200</v>
+        <v>1953900</v>
       </c>
       <c r="E70" t="n">
-        <v>236.807</v>
+        <v>1485.076</v>
       </c>
       <c r="F70" t="n">
-        <v>1419.72</v>
+        <v>1315.69</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2023-06-30</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2029-11-30</t>
+          <t>2027-06-01</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>④호황</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -42759,7 +42759,7 @@
         </is>
       </c>
       <c r="L70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -42772,7 +42772,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>⚠ HD한국조선해양(009540) 공시와 동일 계약 21건(shared_with) — 두 파일을 합산하지 말 것</t>
+          <t>⚠ HD한국조선해양(009540) 공시와 동일 계약 22건(shared_with) — 두 파일을 합산하지 말 것</t>
         </is>
       </c>
     </row>
@@ -50450,7 +50450,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>24923.6</v>
+        <v>25076.7</v>
       </c>
     </row>
     <row r="30">
@@ -50470,7 +50470,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.27</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="32">
@@ -50490,7 +50490,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2481</v>
+        <v>0.2496</v>
       </c>
     </row>
     <row r="34">
@@ -50500,7 +50500,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="35">
@@ -50510,7 +50510,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>277300</v>
+        <v>278300</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20906억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1008억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1007억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20424억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 984억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20405억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 984억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20252억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 995억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20234억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19415억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19397억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18663억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 18646억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17772억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 995억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 17756억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17131억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 995억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 17115억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15788억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 15774억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14003억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 13990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2329,43 +2329,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 87800억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 87799억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 89724억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 89720억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98041억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98036억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 106918억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 106910억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 116368억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 116359억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 120470억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 120459억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 130952억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 130941억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2389,43 +2389,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 87800억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 87799억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 89724억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 89720억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98041억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98036억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 106918억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 106910억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 116368억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 116359억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 120470억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 120459억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 130952억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 130941억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4200,55 +4200,55 @@
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20906억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1008억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1007억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20424억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 984억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20405억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 984억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20252억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 995억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20234억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19415억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19397억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18663억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 18646억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17772억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 995억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 17756억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17131억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 995억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 17115억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15788억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 15774억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14003억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 13990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -5326,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 43건 중 포함 38건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 8.1 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 43건 중 포함 38건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 8.2 백만원</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 175,212억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −9,559억(2026 1,563억 · 2027 3,992억 · 2028 4,003억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 1,563억 vs 989억 · 2027 3,992억 vs 42,994억 · 2028 4,003억 vs 131,229억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 175,212억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −9,551억(2026 1,563억 · 2027 3,989억 · 2028 4,000억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 1,563억 vs 989억 · 2027 3,989억 vs 42,994억 · 2028 4,000억 vs 131,229억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28190.8</v>
+        <v>28187.5</v>
       </c>
     </row>
     <row r="30">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.11</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="32">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="33">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2806</v>
+        <v>0.2805</v>
       </c>
     </row>
     <row r="34">
@@ -7853,7 +7853,7 @@
         <v>131.34</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>4.78</v>
+        <v>7.67</v>
       </c>
       <c r="Z18" s="20" t="n">
         <v>-0</v>
@@ -8556,35 +8556,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8675,35 +8675,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8794,35 +8794,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8913,35 +8913,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9032,35 +9032,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9151,35 +9151,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9270,35 +9270,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9389,35 +9389,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9524,7 +9524,7 @@
         <v>434500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>426000</v>
+        <v>420500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9706,7 +9706,7 @@
         <v>411500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>420500</v>
+        <v>418000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9797,7 +9797,7 @@
         <v>478298.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>429000</v>
+        <v>426166.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11356,36 +11356,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.004400469</v>
+        <v>-0.002387986</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.008435646</v>
+        <v>0.012808585</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.008385864999999999</v>
+        <v>-0.003035742</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5940.239177688</v>
+        <v>5940.251233359</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.008346742000000001</v>
+        <v>0.004346728</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.012736213</v>
+        <v>0.005467482</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.002680009</v>
+        <v>0.002181681</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>5940.251172834</v>
+        <v>5940.248234745</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.002488923</v>
+        <v>0.010132294</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.003923036</v>
+        <v>-0.002218485</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11484,36 +11484,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>0.002999531</v>
+        <v>0.004195828</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.001564354</v>
+        <v>0.00199152</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.008385864999999999</v>
+        <v>0.006117191</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5940.249177688</v>
+        <v>5940.240335402</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.001653258</v>
+        <v>0.003396945</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.012736213</v>
+        <v>0.014453859</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.007319991</v>
+        <v>0.001102488</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>5940.241172834</v>
+        <v>5940.247087978</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.012488923</v>
+        <v>-0.001064827</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.003923036</v>
+        <v>0.006546271</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11743,33 +11743,33 @@
         <v>0.117933641</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.105598445</v>
+        <v>0.105605973</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.099052616</v>
+        <v>0.099026038</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.023370318</v>
+        <v>0.023347032</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.098742735</v>
+        <v>0.098724616</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.095907176</v>
+        <v>0.09589326500000001</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.09317342000000001</v>
+        <v>0.09316292</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.036993179</v>
+        <v>0.036981126</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.091169744</v>
+        <v>0.091164517</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.086211326</v>
+        <v>0.086208624</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11871,33 +11871,33 @@
         <v>0.108137514</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.09768289600000001</v>
+        <v>0.097689861</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.09228847599999999</v>
+        <v>0.092263756</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.021909238</v>
+        <v>0.021887385</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.092701829</v>
+        <v>0.092684591</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.090537521</v>
+        <v>0.090524102</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.08838991</v>
+        <v>0.088379634</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.035248193</v>
+        <v>0.035236578</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.087015649</v>
+        <v>0.087010301</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.082597608</v>
+        <v>0.082594614</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12576,33 +12576,33 @@
         <v>34829.474339</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>34829.475578</v>
+        <v>34829.480349</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>34829.484298</v>
+        <v>34829.486983</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>34829.502342</v>
+        <v>34829.503408</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>34829.43187</v>
+        <v>34829.429477</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>34829.4931</v>
+        <v>34829.488186</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>34829.429217</v>
+        <v>34829.434366</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>34829.435563</v>
+        <v>34829.429314</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>34829.48665</v>
+        <v>34829.487091</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>34829.557384</v>
+        <v>34829.556788</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12877,39 +12877,39 @@
         <v>0.139251906</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.13915298</v>
+        <v>0.139153</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.139153005</v>
+        <v>0.139152905</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.139143594</v>
+        <v>0.139143576</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.139116495</v>
+        <v>0.13911641</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.139096751</v>
+        <v>0.139096704</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.139076865</v>
+        <v>0.139076876</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.139057176</v>
+        <v>0.139057157</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.139007174</v>
+        <v>0.139007152</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.138934301</v>
+        <v>0.138934307</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -13254,7 +13254,7 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>426000</v>
+        <v>420500</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2449400659720531</v>
+        <v>0.2449400283849805</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04875938992436118</v>
+        <v>0.04875939035089232</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>1</v>
+        <v>0.9999998857840945</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.02472798170159547</v>
+        <v>0.024727889526103</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.1390168016479711</v>
+        <v>0.1390139610112214</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42715,91 +42715,91 @@
         <v>1418.75</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Y20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AA20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AC20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AK20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AP20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AQ20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AR20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AS20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AT20" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
     </row>
     <row r="21">
@@ -42853,91 +42853,91 @@
         <v>1439.39</v>
       </c>
       <c r="R21" s="13" t="n">
-        <v>1419.56</v>
+        <v>1418.48</v>
       </c>
       <c r="S21" s="13" t="n">
-        <v>1417.61</v>
+        <v>1416.32</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>1419.38</v>
+        <v>1418.09</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>1423.97</v>
+        <v>1422.68</v>
       </c>
       <c r="V21" s="13" t="n">
-        <v>1425.62</v>
+        <v>1424.33</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>1426.71</v>
+        <v>1425.42</v>
       </c>
       <c r="X21" s="13" t="n">
-        <v>1428.51</v>
+        <v>1427.22</v>
       </c>
       <c r="Y21" s="13" t="n">
-        <v>1428.55</v>
+        <v>1427.26</v>
       </c>
       <c r="Z21" s="13" t="n">
-        <v>1430.42</v>
+        <v>1429.13</v>
       </c>
       <c r="AA21" s="13" t="n">
-        <v>1436.87</v>
+        <v>1435.58</v>
       </c>
       <c r="AB21" s="13" t="n">
-        <v>1434.7</v>
+        <v>1433.41</v>
       </c>
       <c r="AC21" s="13" t="n">
-        <v>1434.51</v>
+        <v>1433.22</v>
       </c>
       <c r="AD21" s="13" t="n">
-        <v>1426.09</v>
+        <v>1424.8</v>
       </c>
       <c r="AE21" s="13" t="n">
-        <v>1422.83</v>
+        <v>1421.54</v>
       </c>
       <c r="AF21" s="13" t="n">
-        <v>1427.01</v>
+        <v>1425.72</v>
       </c>
       <c r="AG21" s="13" t="n">
-        <v>1414.52</v>
+        <v>1413.23</v>
       </c>
       <c r="AH21" s="13" t="n">
-        <v>1399.58</v>
+        <v>1398.29</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1389.11</v>
+        <v>1387.82</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1409.3</v>
+        <v>1408.01</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1418.92</v>
+        <v>1417.63</v>
       </c>
     </row>
     <row r="22">
@@ -42991,91 +42991,91 @@
         <v>2245096.1</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>2285103.3</v>
+        <v>2283364.8</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>2232356.4</v>
+        <v>2230325</v>
       </c>
       <c r="T22" s="18" t="n">
-        <v>2217297.1</v>
+        <v>2215282</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>2135691.5</v>
+        <v>2133756.8</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>2060544.9</v>
+        <v>2058680.4</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>1969290.3</v>
+        <v>1967509.7</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>1905171.9</v>
+        <v>1903451.5</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>1773007.1</v>
+        <v>1771406</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>1594486.2</v>
+        <v>1593048.2</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>1053824.6</v>
+        <v>1052878.5</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>825500.8</v>
+        <v>824758.6</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>676415.8</v>
+        <v>675807.5</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>428183.3</v>
+        <v>427796</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>247801</v>
+        <v>247576.3</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>215525.9</v>
+        <v>215331</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>93150.8</v>
+        <v>93065.8</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>47483.3</v>
+        <v>47439.6</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>38859.7</v>
+        <v>38823.6</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>17650.1</v>
+        <v>17633.9</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>14043.2</v>
+        <v>14030.4</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>14043.2</v>
+        <v>14030.4</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>13888.9</v>
+        <v>13876.3</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>14043.2</v>
+        <v>14030.4</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>12500</v>
+        <v>12488.6</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>251181.4</v>
@@ -43087,28 +43087,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX22" s="18" t="n">
-        <v>7680055.5</v>
+        <v>7678317</v>
       </c>
       <c r="AY22" s="18" t="n">
-        <v>8645889.9</v>
+        <v>8638044.199999999</v>
       </c>
       <c r="AZ22" s="18" t="n">
-        <v>7241955.5</v>
+        <v>7235415.4</v>
       </c>
       <c r="BA22" s="18" t="n">
-        <v>2983924.5</v>
+        <v>2981240.6</v>
       </c>
       <c r="BB22" s="18" t="n">
-        <v>603961</v>
+        <v>603412.7</v>
       </c>
       <c r="BC22" s="18" t="n">
-        <v>84904.8</v>
+        <v>84826.7</v>
       </c>
       <c r="BD22" s="18" t="n">
-        <v>56481.4</v>
+        <v>56430</v>
       </c>
       <c r="BE22" s="18" t="n">
-        <v>54629.6</v>
+        <v>54579.9</v>
       </c>
     </row>
     <row r="23">
@@ -43162,91 +43162,91 @@
         <v>2174443.5</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>2191389.7</v>
+        <v>2189722.5</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>2140805.9</v>
+        <v>2138857.8</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>2124729.4</v>
+        <v>2122798.5</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>2042106.6</v>
+        <v>2040257</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>1966959.9</v>
+        <v>1965180.6</v>
       </c>
       <c r="W23" s="18" t="n">
-        <v>1876722.6</v>
+        <v>1875026.2</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>1812604.2</v>
+        <v>1810968</v>
       </c>
       <c r="Y23" s="18" t="n">
-        <v>1679422.1</v>
+        <v>1677906.2</v>
       </c>
       <c r="Z23" s="18" t="n">
-        <v>1500901.2</v>
+        <v>1499548.4</v>
       </c>
       <c r="AA23" s="18" t="n">
-        <v>962274.1</v>
+        <v>961411.3</v>
       </c>
       <c r="AB23" s="18" t="n">
-        <v>732933.1</v>
+        <v>732275.1</v>
       </c>
       <c r="AC23" s="18" t="n">
-        <v>582830.8</v>
+        <v>582307.7</v>
       </c>
       <c r="AD23" s="18" t="n">
-        <v>334598.4</v>
+        <v>334296.2</v>
       </c>
       <c r="AE23" s="18" t="n">
-        <v>156250.5</v>
+        <v>156109.1</v>
       </c>
       <c r="AF23" s="18" t="n">
-        <v>122958.2</v>
+        <v>122847.5</v>
       </c>
       <c r="AG23" s="18" t="n">
-        <v>39723.2</v>
+        <v>39686.4</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>39723.2</v>
+        <v>39686.4</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>38859.7</v>
+        <v>38823.6</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>17650.1</v>
+        <v>17633.9</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>14043.2</v>
+        <v>14030.4</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>14043.2</v>
+        <v>14030.4</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>13888.9</v>
+        <v>13876.3</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>14043.2</v>
+        <v>14030.4</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>12500</v>
+        <v>12488.6</v>
       </c>
       <c r="AU23" s="18" t="n">
         <v>251181.4</v>
@@ -43258,28 +43258,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>7488623</v>
+        <v>7486955.8</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>8274601.8</v>
+        <v>8267093.9</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>6869650.1</v>
+        <v>6863448.8</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>2612636.4</v>
+        <v>2610290.3</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>358655.1</v>
+        <v>358329.4</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>84904.8</v>
+        <v>84826.7</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>56481.4</v>
+        <v>56430</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>54629.6</v>
+        <v>54579.9</v>
       </c>
     </row>
     <row r="24">
@@ -43333,91 +43333,91 @@
         <v>2118864.6</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>2090620.5</v>
+        <v>2089031</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>2042364.7</v>
+        <v>2040507.4</v>
       </c>
       <c r="T24" s="18" t="n">
-        <v>2025194.4</v>
+        <v>2023355.3</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>1941477.8</v>
+        <v>1939721.1</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>1866331.1</v>
+        <v>1864644.6</v>
       </c>
       <c r="W24" s="18" t="n">
-        <v>1777187.6</v>
+        <v>1775583.1</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>1713069.2</v>
+        <v>1711524.8</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>1578793.3</v>
+        <v>1577370.3</v>
       </c>
       <c r="Z24" s="18" t="n">
-        <v>1400272.4</v>
+        <v>1399012.5</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>863832.9</v>
+        <v>863060.9</v>
       </c>
       <c r="AB24" s="18" t="n">
-        <v>633398.1</v>
+        <v>632831.9</v>
       </c>
       <c r="AC24" s="18" t="n">
-        <v>521308.2</v>
+        <v>520841.8</v>
       </c>
       <c r="AD24" s="18" t="n">
-        <v>281873.4</v>
+        <v>281619.8</v>
       </c>
       <c r="AE24" s="18" t="n">
-        <v>121607</v>
+        <v>121497.6</v>
       </c>
       <c r="AF24" s="18" t="n">
-        <v>122958.2</v>
+        <v>122847.5</v>
       </c>
       <c r="AG24" s="18" t="n">
-        <v>39723.2</v>
+        <v>39686.4</v>
       </c>
       <c r="AH24" s="18" t="n">
-        <v>39723.2</v>
+        <v>39686.4</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>38859.7</v>
+        <v>38823.6</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>17650.1</v>
+        <v>17633.9</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>14043.2</v>
+        <v>14030.4</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>14043.2</v>
+        <v>14030.4</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>13888.9</v>
+        <v>13876.3</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>14043.2</v>
+        <v>14030.4</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>14197.5</v>
+        <v>14184.6</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>12500</v>
+        <v>12488.6</v>
       </c>
     </row>
     <row r="25">
@@ -43471,46 +43471,46 @@
         <v>55578.9</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>100769.2</v>
+        <v>100691.5</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>98441.2</v>
+        <v>98350.39999999999</v>
       </c>
       <c r="T25" s="18" t="n">
-        <v>99535</v>
+        <v>99443.10000000001</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>100628.8</v>
+        <v>100535.9</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>100628.8</v>
+        <v>100535.9</v>
       </c>
       <c r="W25" s="18" t="n">
-        <v>99535</v>
+        <v>99443.10000000001</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>99535</v>
+        <v>99443.10000000001</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>100628.8</v>
+        <v>100535.9</v>
       </c>
       <c r="Z25" s="18" t="n">
-        <v>100628.8</v>
+        <v>100535.9</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>98441.2</v>
+        <v>98350.39999999999</v>
       </c>
       <c r="AB25" s="18" t="n">
-        <v>99535</v>
+        <v>99443.10000000001</v>
       </c>
       <c r="AC25" s="18" t="n">
-        <v>61522.7</v>
+        <v>61465.9</v>
       </c>
       <c r="AD25" s="18" t="n">
-        <v>52725</v>
+        <v>52676.3</v>
       </c>
       <c r="AE25" s="18" t="n">
-        <v>34643.6</v>
+        <v>34611.6</v>
       </c>
       <c r="AF25" s="18" t="n">
         <v>0</v>
@@ -43770,119 +43770,119 @@
         <v/>
       </c>
       <c r="R31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1354.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1351.18)</f>
         <v/>
       </c>
       <c r="S31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="T31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="U31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="V31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="W31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="X31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="Y31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="Z31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AA31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AB31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AC31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AD31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AE31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AF31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AG31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AH31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AI31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AJ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AK31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AL31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AM31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AN31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AO31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AP31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AQ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AR31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AS31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AT31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
     </row>
@@ -56187,7 +56187,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -62088,7 +62088,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1007억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20877억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20405억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 984억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20383억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 982억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20234억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20211억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19397억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19376억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18646억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 18626억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17756억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 17736억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17115억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 17097억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15774억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 15756억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 13975억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80382억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80383억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 87799억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 87797억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 89720억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 89717억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98036억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98030억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 106910억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 106903억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 116359억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 116349억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 120459억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 120447억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 130941억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 130927억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 80382억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 80383억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 87799억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 87797억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 89720억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 89717억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98036억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98030억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 106910억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 106903억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 116359억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 116349억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 120459억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 120447억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 130941억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 130927억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4200,55 +4200,55 @@
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1007억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20877억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20405억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 984억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20383억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 982억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20234억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20211억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19397억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19376억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18646억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 18626억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17756억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 17736억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17115억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 994억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 17097억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15774억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 15756억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1005억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 13975억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -5326,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 43건 중 포함 38건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 8.2 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 43건 중 포함 38건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 8.1 백만원</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 175,212억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −9,551억(2026 1,563억 · 2027 3,989억 · 2028 4,000억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 1,563억 vs 989억 · 2027 3,989억 vs 42,994억 · 2028 4,000억 vs 131,229억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 175,212억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −9,541억(2026 1,562억 · 2027 3,984억 · 2028 3,995억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 1,562억 vs 989억 · 2027 3,984억 vs 42,994억 · 2028 3,995억 vs 131,229억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28187.5</v>
+        <v>28184.2</v>
       </c>
     </row>
     <row r="30">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.92</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="32">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>4.19</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="33">
@@ -7853,7 +7853,7 @@
         <v>131.34</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>7.67</v>
+        <v>11.17</v>
       </c>
       <c r="Z18" s="20" t="n">
         <v>-0</v>
@@ -8556,35 +8556,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8675,35 +8675,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8794,35 +8794,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8913,35 +8913,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9032,35 +9032,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9151,35 +9151,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9270,35 +9270,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9389,35 +9389,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9524,7 +9524,7 @@
         <v>434500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>420500</v>
+        <v>401000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9706,7 +9706,7 @@
         <v>411500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>418000</v>
+        <v>399500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9797,7 +9797,7 @@
         <v>478298.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>426166.7</v>
+        <v>420125</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11356,36 +11356,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.002387986</v>
+        <v>-0.004720743</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.012808585</v>
+        <v>-0.003741612</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.003035742</v>
+        <v>0.004965527</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5940.251233359</v>
+        <v>5940.243551631</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.004346728</v>
+        <v>0.009062983</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.005467482</v>
+        <v>0.003002963</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.002181681</v>
+        <v>-0.004436928</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>5940.248234745</v>
+        <v>5940.247726971</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.010132294</v>
+        <v>0.009001033</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.002218485</v>
+        <v>0.002135544</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11484,36 +11484,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>0.004195828</v>
+        <v>0.001862927</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.00199152</v>
+        <v>-0.004558959</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.006117191</v>
+        <v>0.00411858</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5940.240335402</v>
+        <v>5940.242653783</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.003396945</v>
+        <v>-0.001886713</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.014453859</v>
+        <v>0.00198941</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.001102488</v>
+        <v>0.004483925</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>5940.247087978</v>
+        <v>5940.24658023</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.001064827</v>
+        <v>0.007803912</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.006546271</v>
+        <v>0.000900273</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11743,33 +11743,33 @@
         <v>0.117933641</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.105605973</v>
+        <v>0.105623836</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.099026038</v>
+        <v>0.09899292699999999</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.023347032</v>
+        <v>0.023318929</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.098724616</v>
+        <v>0.098701993</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.09589326500000001</v>
+        <v>0.095875764</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.09316292</v>
+        <v>0.093149775</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.036981126</v>
+        <v>0.036966324</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.091164517</v>
+        <v>0.091157845</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.086208624</v>
+        <v>0.086204829</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11871,33 +11871,33 @@
         <v>0.108137514</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.097689861</v>
+        <v>0.09770638399999999</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.092263756</v>
+        <v>0.09223300800000001</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.021887385</v>
+        <v>0.021861019</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.092684591</v>
+        <v>0.092663117</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.090524102</v>
+        <v>0.090507266</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.088379634</v>
+        <v>0.08836681</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.035236578</v>
+        <v>0.035222325</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.087010301</v>
+        <v>0.08700352</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.082594614</v>
+        <v>0.082590672</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12576,33 +12576,33 @@
         <v>34829.474339</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>34829.480349</v>
+        <v>34829.477512</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>34829.486983</v>
+        <v>34829.486974</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>34829.503408</v>
+        <v>34829.503766</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>34829.429477</v>
+        <v>34829.434025</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>34829.488186</v>
+        <v>34829.493173</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>34829.434366</v>
+        <v>34829.427802</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>34829.429314</v>
+        <v>34829.435478</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>34829.487091</v>
+        <v>34829.495997</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>34829.556788</v>
+        <v>34829.553277</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12877,39 +12877,39 @@
         <v>0.139251906</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.139153</v>
+        <v>0.139152912</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.139152905</v>
+        <v>0.139152996</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.139143576</v>
+        <v>0.139143489</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.13911641</v>
+        <v>0.139116482</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.139096704</v>
+        <v>0.139096651</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.139076876</v>
+        <v>0.139076869</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.139057157</v>
+        <v>0.13905711</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.139007152</v>
+        <v>0.139007163</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.138934307</v>
+        <v>0.138934277</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -13254,11 +13254,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>420500</v>
+        <v>401000</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 431,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 426,000원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2449400283849805</v>
+        <v>0.2449400587259394</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04875939035089232</v>
+        <v>0.04875935972933527</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999998857840945</v>
+        <v>0.9999998857638707</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.024727889526103</v>
+        <v>0.02472807226453414</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.1390139610112214</v>
+        <v>0.1390183386268878</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42715,91 +42715,91 @@
         <v>1418.75</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Y20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AA20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AC20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AK20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AP20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AQ20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AR20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AS20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AT20" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
     </row>
     <row r="21">
@@ -42853,91 +42853,91 @@
         <v>1439.39</v>
       </c>
       <c r="R21" s="13" t="n">
-        <v>1418.48</v>
+        <v>1417.55</v>
       </c>
       <c r="S21" s="13" t="n">
-        <v>1416.32</v>
+        <v>1414.76</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>1418.09</v>
+        <v>1416.53</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>1422.68</v>
+        <v>1421.12</v>
       </c>
       <c r="V21" s="13" t="n">
-        <v>1424.33</v>
+        <v>1422.77</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>1425.42</v>
+        <v>1423.86</v>
       </c>
       <c r="X21" s="13" t="n">
-        <v>1427.22</v>
+        <v>1425.66</v>
       </c>
       <c r="Y21" s="13" t="n">
-        <v>1427.26</v>
+        <v>1425.7</v>
       </c>
       <c r="Z21" s="13" t="n">
-        <v>1429.13</v>
+        <v>1427.57</v>
       </c>
       <c r="AA21" s="13" t="n">
-        <v>1435.58</v>
+        <v>1434.02</v>
       </c>
       <c r="AB21" s="13" t="n">
-        <v>1433.41</v>
+        <v>1431.85</v>
       </c>
       <c r="AC21" s="13" t="n">
-        <v>1433.22</v>
+        <v>1431.66</v>
       </c>
       <c r="AD21" s="13" t="n">
-        <v>1424.8</v>
+        <v>1423.24</v>
       </c>
       <c r="AE21" s="13" t="n">
-        <v>1421.54</v>
+        <v>1419.98</v>
       </c>
       <c r="AF21" s="13" t="n">
-        <v>1425.72</v>
+        <v>1424.16</v>
       </c>
       <c r="AG21" s="13" t="n">
-        <v>1413.23</v>
+        <v>1411.67</v>
       </c>
       <c r="AH21" s="13" t="n">
-        <v>1398.29</v>
+        <v>1396.73</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1387.82</v>
+        <v>1386.26</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1408.01</v>
+        <v>1406.45</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1417.63</v>
+        <v>1416.07</v>
       </c>
     </row>
     <row r="22">
@@ -42991,91 +42991,91 @@
         <v>2245096.1</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>2283364.8</v>
+        <v>2281867.8</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>2230325</v>
+        <v>2227868.4</v>
       </c>
       <c r="T22" s="18" t="n">
-        <v>2215282</v>
+        <v>2212845</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>2133756.8</v>
+        <v>2131417.1</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>2058680.4</v>
+        <v>2056425.6</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>1967509.7</v>
+        <v>1965356.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>1903451.5</v>
+        <v>1901370.9</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>1771406</v>
+        <v>1769469.8</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>1593048.2</v>
+        <v>1591309.3</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>1052878.5</v>
+        <v>1051734.4</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>824758.6</v>
+        <v>823861</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>675807.5</v>
+        <v>675071.9</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>427796</v>
+        <v>427327.6</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>247576.3</v>
+        <v>247304.7</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>215331</v>
+        <v>215095.4</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>93065.8</v>
+        <v>92963.10000000001</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>47439.6</v>
+        <v>47386.6</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>38823.6</v>
+        <v>38780</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>17633.9</v>
+        <v>17614.4</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>14030.4</v>
+        <v>14015</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>14030.4</v>
+        <v>14015</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>13876.3</v>
+        <v>13861</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>14030.4</v>
+        <v>14015</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>12488.6</v>
+        <v>12474.9</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>251181.4</v>
@@ -43087,28 +43087,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX22" s="18" t="n">
-        <v>7678317</v>
+        <v>7676820</v>
       </c>
       <c r="AY22" s="18" t="n">
-        <v>8638044.199999999</v>
+        <v>8628556.1</v>
       </c>
       <c r="AZ22" s="18" t="n">
-        <v>7235415.4</v>
+        <v>7227506.4</v>
       </c>
       <c r="BA22" s="18" t="n">
-        <v>2981240.6</v>
+        <v>2977994.9</v>
       </c>
       <c r="BB22" s="18" t="n">
-        <v>603412.7</v>
+        <v>602749.8</v>
       </c>
       <c r="BC22" s="18" t="n">
-        <v>84826.7</v>
+        <v>84732.39999999999</v>
       </c>
       <c r="BD22" s="18" t="n">
-        <v>56430</v>
+        <v>56368</v>
       </c>
       <c r="BE22" s="18" t="n">
-        <v>54579.9</v>
+        <v>54519.9</v>
       </c>
     </row>
     <row r="23">
@@ -43162,91 +43162,91 @@
         <v>2174443.5</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>2189722.5</v>
+        <v>2188286.8</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>2138857.8</v>
+        <v>2136501.9</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>2122798.5</v>
+        <v>2120463.3</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>2040257</v>
+        <v>2038020.2</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>1965180.6</v>
+        <v>1963028.7</v>
       </c>
       <c r="W23" s="18" t="n">
-        <v>1875026.2</v>
+        <v>1872974.8</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>1810968</v>
+        <v>1808989.3</v>
       </c>
       <c r="Y23" s="18" t="n">
-        <v>1677906.2</v>
+        <v>1676073</v>
       </c>
       <c r="Z23" s="18" t="n">
-        <v>1499548.4</v>
+        <v>1497912.4</v>
       </c>
       <c r="AA23" s="18" t="n">
-        <v>961411.3</v>
+        <v>960367.9</v>
       </c>
       <c r="AB23" s="18" t="n">
-        <v>732275.1</v>
+        <v>731479.3</v>
       </c>
       <c r="AC23" s="18" t="n">
-        <v>582307.7</v>
+        <v>581675</v>
       </c>
       <c r="AD23" s="18" t="n">
-        <v>334296.2</v>
+        <v>333930.7</v>
       </c>
       <c r="AE23" s="18" t="n">
-        <v>156109.1</v>
+        <v>155938.2</v>
       </c>
       <c r="AF23" s="18" t="n">
-        <v>122847.5</v>
+        <v>122713.8</v>
       </c>
       <c r="AG23" s="18" t="n">
-        <v>39686.4</v>
+        <v>39641.7</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>39686.4</v>
+        <v>39641.7</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>38823.6</v>
+        <v>38780</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>17633.9</v>
+        <v>17614.4</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>14030.4</v>
+        <v>14015</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>14030.4</v>
+        <v>14015</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>13876.3</v>
+        <v>13861</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>14030.4</v>
+        <v>14015</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>12488.6</v>
+        <v>12474.9</v>
       </c>
       <c r="AU23" s="18" t="n">
         <v>251181.4</v>
@@ -43258,28 +43258,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>7486955.8</v>
+        <v>7485520.1</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>8267093.9</v>
+        <v>8258014.1</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>6863448.8</v>
+        <v>6855949.5</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>2610290.3</v>
+        <v>2607452.9</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>358329.4</v>
+        <v>357935.4</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>84826.7</v>
+        <v>84732.39999999999</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>56430</v>
+        <v>56368</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>54579.9</v>
+        <v>54519.9</v>
       </c>
     </row>
     <row r="24">
@@ -43333,91 +43333,91 @@
         <v>2118864.6</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>2089031</v>
+        <v>2087662.3</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>2040507.4</v>
+        <v>2038261.4</v>
       </c>
       <c r="T24" s="18" t="n">
-        <v>2023355.3</v>
+        <v>2021131.3</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>1939721.1</v>
+        <v>1937596.6</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>1864644.6</v>
+        <v>1862605.1</v>
       </c>
       <c r="W24" s="18" t="n">
-        <v>1775583.1</v>
+        <v>1773642.7</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>1711524.8</v>
+        <v>1709657.2</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>1577370.3</v>
+        <v>1575649.4</v>
       </c>
       <c r="Z24" s="18" t="n">
-        <v>1399012.5</v>
+        <v>1397488.8</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>863060.9</v>
+        <v>862127.4</v>
       </c>
       <c r="AB24" s="18" t="n">
-        <v>632831.9</v>
+        <v>632147.2</v>
       </c>
       <c r="AC24" s="18" t="n">
-        <v>520841.8</v>
+        <v>520277.8</v>
       </c>
       <c r="AD24" s="18" t="n">
-        <v>281619.8</v>
+        <v>281313.3</v>
       </c>
       <c r="AE24" s="18" t="n">
-        <v>121497.6</v>
+        <v>121365.2</v>
       </c>
       <c r="AF24" s="18" t="n">
-        <v>122847.5</v>
+        <v>122713.8</v>
       </c>
       <c r="AG24" s="18" t="n">
-        <v>39686.4</v>
+        <v>39641.7</v>
       </c>
       <c r="AH24" s="18" t="n">
-        <v>39686.4</v>
+        <v>39641.7</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>38823.6</v>
+        <v>38780</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>17633.9</v>
+        <v>17614.4</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>14030.4</v>
+        <v>14015</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>14030.4</v>
+        <v>14015</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>13876.3</v>
+        <v>13861</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>14030.4</v>
+        <v>14015</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>14184.6</v>
+        <v>14169</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>12488.6</v>
+        <v>12474.9</v>
       </c>
     </row>
     <row r="25">
@@ -43471,46 +43471,46 @@
         <v>55578.9</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>100691.5</v>
+        <v>100624.5</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>98350.39999999999</v>
+        <v>98240.5</v>
       </c>
       <c r="T25" s="18" t="n">
-        <v>99443.10000000001</v>
+        <v>99332</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>100535.9</v>
+        <v>100423.6</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>100535.9</v>
+        <v>100423.6</v>
       </c>
       <c r="W25" s="18" t="n">
-        <v>99443.10000000001</v>
+        <v>99332</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>99443.10000000001</v>
+        <v>99332</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>100535.9</v>
+        <v>100423.6</v>
       </c>
       <c r="Z25" s="18" t="n">
-        <v>100535.9</v>
+        <v>100423.6</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>98350.39999999999</v>
+        <v>98240.5</v>
       </c>
       <c r="AB25" s="18" t="n">
-        <v>99443.10000000001</v>
+        <v>99332</v>
       </c>
       <c r="AC25" s="18" t="n">
-        <v>61465.9</v>
+        <v>61397.2</v>
       </c>
       <c r="AD25" s="18" t="n">
-        <v>52676.3</v>
+        <v>52617.5</v>
       </c>
       <c r="AE25" s="18" t="n">
-        <v>34611.6</v>
+        <v>34572.9</v>
       </c>
       <c r="AF25" s="18" t="n">
         <v>0</v>
@@ -43770,119 +43770,119 @@
         <v/>
       </c>
       <c r="R31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1351.18)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1348.08)</f>
         <v/>
       </c>
       <c r="S31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="T31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="U31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="V31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="W31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="X31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="Y31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="Z31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AA31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AB31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AC31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AD31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AE31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AF31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AG31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AH31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AI31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AJ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AK31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AL31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AM31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AN31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AO31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AP31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AQ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AR31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AS31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AT31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
     </row>
@@ -56187,7 +56187,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -62088,7 +62088,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -2191,121 +2191,121 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 96% × 코호트 15.0% + 등급없음 4% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.9%(코호트 모드 reference_anchor; 등급 비중 96% × 코호트 10.8% + 등급없음 4% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 94% × 코호트 15.0% + 등급없음 6% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 94% × 코호트 10.8% + 등급없음 6% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 94% × 코호트 15.0% + 등급없음 6% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 94% × 코호트 10.8% + 등급없음 6% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 93% × 코호트 15.0% + 등급없음 7% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 93% × 코호트 10.8% + 등급없음 7% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 96% × 코호트 15.0% + 등급없음 4% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 10.9%(코호트 모드 reference_anchor; 등급 비중 96% × 코호트 10.8% + 등급없음 4% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 10.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 10.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 94% × 코호트 15.0% + 등급없음 6% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 94% × 코호트 10.8% + 등급없음 6% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 94% × 코호트 15.0% + 등급없음 6% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 94% × 코호트 10.8% + 등급없음 6% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 93% × 코호트 15.0% + 등급없음 7% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 -1.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%)
+        <t>추정: SLS 코호트 타겟 11.0%(코호트 모드 reference_anchor; 등급 비중 93% × 코호트 10.8% + 등급없음 7% × 최근 4분기 실측 OPM 중위 14.0%) + 회사 캘리브레이션 +3.1%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%)
 [divide]</t>
       </text>
     </comment>
@@ -2317,55 +2317,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 73228억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 73295억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80383억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80538억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 87797억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 88043억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 89717억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90061억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98030억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98486억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 106903억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107482억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 116349억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117066억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 120447억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121315억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 130927억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131968억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2377,55 +2377,55 @@
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 73228억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 73295억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 80383억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 80538억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 87797억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 88043억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 89717억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 90061억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98030억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98486억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 106903억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 107482억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 116349억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 117066억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 120447억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 121315억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 130927억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 131968억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -5326,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 14.96%→14.93%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 175,212억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −9,541억(2026 1,562억 · 2027 3,984억 · 2028 3,995억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 1,562억 vs 989억 · 2027 3,984억 vs 42,994억 · 2028 3,995억 vs 131,229억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 175,212억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −9,541억(2026 1,562억 · 2027 3,984억 · 2028 3,995억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 1,562억 vs 989억 · 2027 3,984억 vs 42,994억 · 2028 3,995억 vs 131,229억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28184.2</v>
+        <v>28512.2</v>
       </c>
     </row>
     <row r="30">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.23</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="32">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2805</v>
+        <v>0.2838</v>
       </c>
     </row>
     <row r="34">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="35">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>313500</v>
+        <v>316500</v>
       </c>
     </row>
     <row r="36">
@@ -11356,36 +11356,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.004720743</v>
+        <v>0.004003777</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.003741612</v>
+        <v>-0.005569764</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.004965527</v>
+        <v>0.006918614</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5940.243551631</v>
+        <v>5940.248772391</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.009062983</v>
+        <v>0.000570888</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.003002963</v>
+        <v>0.00383696</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.004436928</v>
+        <v>0.014627076</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>5940.247726971</v>
+        <v>5940.240432627</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.009001033</v>
+        <v>0.007424839</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.002135544</v>
+        <v>-0.004159396</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11484,36 +11484,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>0.001862927</v>
+        <v>0.001403777</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.004558959</v>
+        <v>0.004430236</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.00411858</v>
+        <v>-0.003081386</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5940.242653783</v>
+        <v>5940.258772391</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.001886713</v>
+        <v>0.000570888</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.00198941</v>
+        <v>0.00383696</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.004483925</v>
+        <v>0.004627076</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>5940.24658023</v>
+        <v>5940.250432627</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.007803912</v>
+        <v>0.007424839</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.000900273</v>
+        <v>-0.004159396</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11740,36 +11740,36 @@
         <v/>
       </c>
       <c r="AC33" s="31" t="n">
-        <v>0.117933641</v>
+        <v>0.119035577</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.105623836</v>
+        <v>0.106813072</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.09899292699999999</v>
+        <v>0.100002265</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.023318929</v>
+        <v>0.024445289</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.098701993</v>
+        <v>0.099615368</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.095875764</v>
+        <v>0.096736929</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.093149775</v>
+        <v>0.09396531900000001</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.036966324</v>
+        <v>0.03808628</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.091157845</v>
+        <v>0.09197076999999999</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.086204829</v>
+        <v>0.08708323900000001</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11868,36 +11868,36 @@
         <v/>
       </c>
       <c r="AC34" s="31" t="n">
-        <v>0.108137514</v>
+        <v>0.109147918</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.09770638399999999</v>
+        <v>0.09881377</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.09223300800000001</v>
+        <v>0.093186519</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.021861019</v>
+        <v>0.02292122</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.092663117</v>
+        <v>0.093543903</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.090507266</v>
+        <v>0.09134526</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.08836681</v>
+        <v>0.08916647799999999</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.035222325</v>
+        <v>0.036300438</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.08700352</v>
+        <v>0.08780937799999999</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.082590672</v>
+        <v>0.08346105400000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12874,42 +12874,42 @@
         <v/>
       </c>
       <c r="AC42" s="31" t="n">
-        <v>0.139251906</v>
+        <v>0.140604326</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.139152912</v>
+        <v>0.140904377</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.139152996</v>
+        <v>0.140904407</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.139143489</v>
+        <v>0.140932787</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.139116482</v>
+        <v>0.141014835</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.139096651</v>
+        <v>0.141074899</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.139076869</v>
+        <v>0.141134978</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.13905711</v>
+        <v>0.14119487</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.139007163</v>
+        <v>0.141346579</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.138934277</v>
+        <v>0.141567632</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -13148,42 +13148,42 @@
         <v/>
       </c>
       <c r="AC44" s="31" t="n">
-        <v>0.139251901</v>
+        <v>0.140604286</v>
       </c>
       <c r="AD44" s="31" t="n">
-        <v>0.139152712</v>
+        <v>0.140903986</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE44/subQ!AE43,"")</f>
         <v/>
       </c>
       <c r="AF44" s="31" t="n">
-        <v>0.139152712</v>
+        <v>0.140903986</v>
       </c>
       <c r="AG44" s="31" t="n">
-        <v>0.139143113</v>
+        <v>0.140932783</v>
       </c>
       <c r="AH44" s="31" t="n">
-        <v>0.139116449</v>
+        <v>0.141014907</v>
       </c>
       <c r="AI44" s="31" t="n">
-        <v>0.139097251</v>
+        <v>0.141074634</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ44/subQ!AJ43,"")</f>
         <v/>
       </c>
       <c r="AK44" s="31" t="n">
-        <v>0.139076987</v>
+        <v>0.141135427</v>
       </c>
       <c r="AL44" s="31" t="n">
-        <v>0.139056722</v>
+        <v>0.141195154</v>
       </c>
       <c r="AM44" s="31" t="n">
-        <v>0.139007661</v>
+        <v>0.141346604</v>
       </c>
       <c r="AN44" s="31" t="n">
-        <v>0.138934069</v>
+        <v>0.14156738</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO44/subQ!AO43,"")</f>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2449400587259394</v>
+        <v>0.2449401398181984</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999998857638707</v>
+        <v>1</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.02472807226453414</v>
+        <v>0.02472789832762365</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.1390183386268878</v>
+        <v>0.1390141418991683</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40528,7 +40528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>코호트 표(가정): ①적자 −5% ②BEP 0% ③중마진 5% ④호황 10% ⑤초호황 15% — 회사별 캘리브레이션은 target_opm.basis 참조 · 코호트 모드 reference_anchor(대안 ledger_relative) · 잔고 캡 미적용</t>
+          <t>코호트 표(레퍼런스 실측 캘리브레이션): ①적자 −1.1% ②BEP 1% ③중마진 4.3% ④호황 5.4% ⑤초호황 10.8% — 회사별 캘리브레이션은 target_opm.basis 참조 · 코호트 모드 reference_anchor(대안 ledger_relative) · 잔고 캡 미적용</t>
         </is>
       </c>
     </row>
@@ -43570,100 +43570,100 @@
         </is>
       </c>
       <c r="E26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="J26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="K26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="L26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="M26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="N26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="O26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="P26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="Q26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="R26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="S26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="T26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="U26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="V26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="W26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="X26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="Y26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="Z26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AA26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AB26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AC26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AD26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AE26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AF26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AG26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AH26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AI26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AJ26" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="28">
@@ -54493,7 +54493,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트 OPM 표 assumed 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 바꾸려면 --opm-table reference_calibrated(오너 결정 — 하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
+          <t>⚠ 코호트 OPM 표 reference_calibrated 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(이전 가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 다른 표는 --opm-table assumed (하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
         </is>
       </c>
     </row>

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -1648,13 +1648,13 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20877억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20383억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 982억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20382억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 982억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
@@ -1684,7 +1684,7 @@
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17097억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 17096억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80538억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80537억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 88043억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 88042억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90061억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90060억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98486억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98485억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107482억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107481억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117066억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117064억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121315억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121314억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131968억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131967억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 80538억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 80537억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 88043억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 88042억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 90061억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 90060억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98486억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98485억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 107482억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 107481억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 117066억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 117064억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 121315억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 121314억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 131968억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 131967억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4200,13 +4200,13 @@
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20877억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20383억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 982억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20382억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 982억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -4236,7 +4236,7 @@
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17097억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 17096억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28512.2</v>
+        <v>28511.3</v>
       </c>
     </row>
     <row r="30">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.06</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="32">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.99</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="33">
@@ -7853,7 +7853,7 @@
         <v>131.34</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>11.17</v>
+        <v>11.23</v>
       </c>
       <c r="Z18" s="20" t="n">
         <v>-0</v>
@@ -8556,35 +8556,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8675,35 +8675,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8794,35 +8794,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8913,35 +8913,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9032,35 +9032,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9151,35 +9151,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9270,35 +9270,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9389,35 +9389,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9524,7 +9524,7 @@
         <v>434500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>401000</v>
+        <v>384500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9706,7 +9706,7 @@
         <v>411500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>399500</v>
+        <v>383000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9797,7 +9797,7 @@
         <v>478298.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>420125</v>
+        <v>412700</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11356,36 +11356,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>0.004003777</v>
+        <v>0.003553611</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.005569764</v>
+        <v>-0.00380716</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.006918614</v>
+        <v>-0.002797985</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5940.248772391</v>
+        <v>5940.248833788</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.000570888</v>
+        <v>-0.002078367</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.00383696</v>
+        <v>0.0010213</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.014627076</v>
+        <v>0.011516221</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>5940.240432627</v>
+        <v>5940.244676766</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.007424839</v>
+        <v>0.003900756</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.004159396</v>
+        <v>-0.002811777</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11484,36 +11484,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>0.001403777</v>
+        <v>-0.000671277</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.004430236</v>
+        <v>-0.005438573</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.003081386</v>
+        <v>0.005511294</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5940.258772391</v>
+        <v>5940.237040959</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.000570888</v>
+        <v>0.006023743</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.00383696</v>
+        <v>-0.001005347</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.004627076</v>
+        <v>0.009357202</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>5940.250432627</v>
+        <v>5940.242381229</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.007424839</v>
+        <v>0.001500954</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.004159396</v>
+        <v>-0.005293033</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11743,33 +11743,33 @@
         <v>0.119035577</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.106813072</v>
+        <v>0.106800684</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.100002265</v>
+        <v>0.100002852</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.024445289</v>
+        <v>0.024444944</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.099615368</v>
+        <v>0.099615991</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.096736929</v>
+        <v>0.096737508</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.09396531900000001</v>
+        <v>0.093965857</v>
       </c>
       <c r="AL33" s="31" t="n">
         <v>0.03808628</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.09197076999999999</v>
+        <v>0.09197129</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.08708323900000001</v>
+        <v>0.087083779</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11871,33 +11871,33 @@
         <v>0.109147918</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.09881377</v>
+        <v>0.09880231</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.093186519</v>
+        <v>0.093186994</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.02292122</v>
+        <v>0.022920881</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.093543903</v>
+        <v>0.093544425</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.09134526</v>
+        <v>0.091345754</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.08916647799999999</v>
+        <v>0.089166944</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.036300438</v>
+        <v>0.036300422</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.08780937799999999</v>
+        <v>0.087809838</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.08346105400000001</v>
+        <v>0.083461541</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12576,33 +12576,33 @@
         <v>34829.474339</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>34829.477512</v>
+        <v>34829.478114</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>34829.486974</v>
+        <v>34829.485704</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>34829.503766</v>
+        <v>34829.508695</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>34829.434025</v>
+        <v>34829.431719</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>34829.493173</v>
+        <v>34829.496163</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>34829.427802</v>
+        <v>34829.433631</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>34829.435478</v>
+        <v>34829.42872</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>34829.495997</v>
+        <v>34829.493844</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>34829.553277</v>
+        <v>34829.556985</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12877,39 +12877,39 @@
         <v>0.140604326</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.140904377</v>
+        <v>0.140904368</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.140904407</v>
+        <v>0.140904321</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.140932787</v>
+        <v>0.140932684</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.141014835</v>
+        <v>0.141014867</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.141074899</v>
+        <v>0.141074891</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.141134978</v>
+        <v>0.141134933</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.14119487</v>
+        <v>0.14119495</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.141346579</v>
+        <v>0.141346491</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.141567632</v>
+        <v>0.141567708</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -13254,11 +13254,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>401000</v>
+        <v>384500</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 426,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 420,500원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2449401398181984</v>
+        <v>0.2449401802883696</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04875935972933527</v>
+        <v>0.04875938193014453</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>1</v>
+        <v>0.9999997747206621</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.02472789832762365</v>
+        <v>0.02472789423886327</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.1390141418991683</v>
+        <v>0.139014154620006</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -42715,91 +42715,91 @@
         <v>1418.75</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Y20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AA20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AC20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AK20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AP20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AQ20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AR20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AS20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AT20" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
     </row>
     <row r="21">
@@ -42853,91 +42853,91 @@
         <v>1439.39</v>
       </c>
       <c r="R21" s="13" t="n">
-        <v>1417.55</v>
+        <v>1416.98</v>
       </c>
       <c r="S21" s="13" t="n">
-        <v>1414.76</v>
+        <v>1414.73</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>1416.53</v>
+        <v>1416.51</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>1421.12</v>
+        <v>1421.09</v>
       </c>
       <c r="V21" s="13" t="n">
-        <v>1422.77</v>
+        <v>1422.75</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>1423.86</v>
+        <v>1423.84</v>
       </c>
       <c r="X21" s="13" t="n">
-        <v>1425.66</v>
+        <v>1425.63</v>
       </c>
       <c r="Y21" s="13" t="n">
-        <v>1425.7</v>
+        <v>1425.67</v>
       </c>
       <c r="Z21" s="13" t="n">
-        <v>1427.57</v>
+        <v>1427.55</v>
       </c>
       <c r="AA21" s="13" t="n">
-        <v>1434.02</v>
+        <v>1433.99</v>
       </c>
       <c r="AB21" s="13" t="n">
-        <v>1431.85</v>
+        <v>1431.82</v>
       </c>
       <c r="AC21" s="13" t="n">
-        <v>1431.66</v>
+        <v>1431.63</v>
       </c>
       <c r="AD21" s="13" t="n">
-        <v>1423.24</v>
+        <v>1423.21</v>
       </c>
       <c r="AE21" s="13" t="n">
-        <v>1419.98</v>
+        <v>1419.95</v>
       </c>
       <c r="AF21" s="13" t="n">
-        <v>1424.16</v>
+        <v>1424.14</v>
       </c>
       <c r="AG21" s="13" t="n">
-        <v>1411.67</v>
+        <v>1411.65</v>
       </c>
       <c r="AH21" s="13" t="n">
-        <v>1396.73</v>
+        <v>1396.7</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1386.26</v>
+        <v>1386.24</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1406.45</v>
+        <v>1406.42</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1416.07</v>
+        <v>1416.04</v>
       </c>
     </row>
     <row r="22">
@@ -42991,91 +42991,91 @@
         <v>2245096.1</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>2281867.8</v>
+        <v>2280959.9</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>2227868.4</v>
+        <v>2227825.9</v>
       </c>
       <c r="T22" s="18" t="n">
-        <v>2212845</v>
+        <v>2212802.8</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>2131417.1</v>
+        <v>2131376.6</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>2056425.6</v>
+        <v>2056386.6</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>1965356.4</v>
+        <v>1965319.2</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>1901370.9</v>
+        <v>1901334.9</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>1769469.8</v>
+        <v>1769436.3</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>1591309.3</v>
+        <v>1591279.2</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>1051734.4</v>
+        <v>1051714.6</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>823861</v>
+        <v>823845.4</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>675071.9</v>
+        <v>675059.2</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>427327.6</v>
+        <v>427319.5</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>247304.7</v>
+        <v>247299.9</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>215095.4</v>
+        <v>215091.3</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>92963.10000000001</v>
+        <v>92961.3</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>47386.6</v>
+        <v>47385.7</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>38780</v>
+        <v>38779.2</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>17614.4</v>
+        <v>17614.1</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>14015</v>
+        <v>14014.7</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>14015</v>
+        <v>14014.7</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>13861</v>
+        <v>13860.7</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>14015</v>
+        <v>14014.7</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>12474.9</v>
+        <v>12474.7</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>251181.4</v>
@@ -43087,28 +43087,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX22" s="18" t="n">
-        <v>7676820</v>
+        <v>7675912.1</v>
       </c>
       <c r="AY22" s="18" t="n">
-        <v>8628556.1</v>
+        <v>8628391.9</v>
       </c>
       <c r="AZ22" s="18" t="n">
-        <v>7227506.4</v>
+        <v>7227369.6</v>
       </c>
       <c r="BA22" s="18" t="n">
-        <v>2977994.9</v>
+        <v>2977938.7</v>
       </c>
       <c r="BB22" s="18" t="n">
-        <v>602749.8</v>
+        <v>602738.2</v>
       </c>
       <c r="BC22" s="18" t="n">
-        <v>84732.39999999999</v>
+        <v>84730.7</v>
       </c>
       <c r="BD22" s="18" t="n">
-        <v>56368</v>
+        <v>56366.8</v>
       </c>
       <c r="BE22" s="18" t="n">
-        <v>54519.9</v>
+        <v>54518.8</v>
       </c>
     </row>
     <row r="23">
@@ -43162,91 +43162,91 @@
         <v>2174443.5</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>2188286.8</v>
+        <v>2187416.1</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>2136501.9</v>
+        <v>2136461.2</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>2120463.3</v>
+        <v>2120422.9</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>2038020.2</v>
+        <v>2037981.5</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>1963028.7</v>
+        <v>1962991.5</v>
       </c>
       <c r="W23" s="18" t="n">
-        <v>1872974.8</v>
+        <v>1872939.3</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>1808989.3</v>
+        <v>1808955</v>
       </c>
       <c r="Y23" s="18" t="n">
-        <v>1676073</v>
+        <v>1676041.3</v>
       </c>
       <c r="Z23" s="18" t="n">
-        <v>1497912.4</v>
+        <v>1497884.1</v>
       </c>
       <c r="AA23" s="18" t="n">
-        <v>960367.9</v>
+        <v>960349.8</v>
       </c>
       <c r="AB23" s="18" t="n">
-        <v>731479.3</v>
+        <v>731465.5</v>
       </c>
       <c r="AC23" s="18" t="n">
-        <v>581675</v>
+        <v>581664.1</v>
       </c>
       <c r="AD23" s="18" t="n">
-        <v>333930.7</v>
+        <v>333924.4</v>
       </c>
       <c r="AE23" s="18" t="n">
-        <v>155938.2</v>
+        <v>155935.2</v>
       </c>
       <c r="AF23" s="18" t="n">
-        <v>122713.8</v>
+        <v>122711.4</v>
       </c>
       <c r="AG23" s="18" t="n">
-        <v>39641.7</v>
+        <v>39641</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>39641.7</v>
+        <v>39641</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>38780</v>
+        <v>38779.2</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>17614.4</v>
+        <v>17614.1</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>14015</v>
+        <v>14014.7</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>14015</v>
+        <v>14014.7</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>13861</v>
+        <v>13860.7</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>14015</v>
+        <v>14014.7</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>12474.9</v>
+        <v>12474.7</v>
       </c>
       <c r="AU23" s="18" t="n">
         <v>251181.4</v>
@@ -43258,28 +43258,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>7485520.1</v>
+        <v>7484649.4</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>8258014.1</v>
+        <v>8257857.1</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>6855949.5</v>
+        <v>6855819.7</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>2607452.9</v>
+        <v>2607403.8</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>357935.4</v>
+        <v>357928.6</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>84732.39999999999</v>
+        <v>84730.7</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>56368</v>
+        <v>56366.8</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>54519.9</v>
+        <v>54518.8</v>
       </c>
     </row>
     <row r="24">
@@ -43333,91 +43333,91 @@
         <v>2118864.6</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>2087662.3</v>
+        <v>2086832.2</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>2038261.4</v>
+        <v>2038222.6</v>
       </c>
       <c r="T24" s="18" t="n">
-        <v>2021131.3</v>
+        <v>2021092.8</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>1937596.6</v>
+        <v>1937559.8</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>1862605.1</v>
+        <v>1862569.8</v>
       </c>
       <c r="W24" s="18" t="n">
-        <v>1773642.7</v>
+        <v>1773609.1</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>1709657.2</v>
+        <v>1709624.9</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>1575649.4</v>
+        <v>1575619.6</v>
       </c>
       <c r="Z24" s="18" t="n">
-        <v>1397488.8</v>
+        <v>1397462.4</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>862127.4</v>
+        <v>862111.2</v>
       </c>
       <c r="AB24" s="18" t="n">
-        <v>632147.2</v>
+        <v>632135.4</v>
       </c>
       <c r="AC24" s="18" t="n">
-        <v>520277.8</v>
+        <v>520268.1</v>
       </c>
       <c r="AD24" s="18" t="n">
-        <v>281313.3</v>
+        <v>281307.9</v>
       </c>
       <c r="AE24" s="18" t="n">
-        <v>121365.2</v>
+        <v>121363</v>
       </c>
       <c r="AF24" s="18" t="n">
-        <v>122713.8</v>
+        <v>122711.4</v>
       </c>
       <c r="AG24" s="18" t="n">
-        <v>39641.7</v>
+        <v>39641</v>
       </c>
       <c r="AH24" s="18" t="n">
-        <v>39641.7</v>
+        <v>39641</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>38780</v>
+        <v>38779.2</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>17614.4</v>
+        <v>17614.1</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>14015</v>
+        <v>14014.7</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>14015</v>
+        <v>14014.7</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>13861</v>
+        <v>13860.7</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>14015</v>
+        <v>14014.7</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>14169</v>
+        <v>14168.7</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>12474.9</v>
+        <v>12474.7</v>
       </c>
     </row>
     <row r="25">
@@ -43471,46 +43471,46 @@
         <v>55578.9</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>100624.5</v>
+        <v>100583.9</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>98240.5</v>
+        <v>98238.60000000001</v>
       </c>
       <c r="T25" s="18" t="n">
-        <v>99332</v>
+        <v>99330.10000000001</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>100423.6</v>
+        <v>100421.7</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>100423.6</v>
+        <v>100421.7</v>
       </c>
       <c r="W25" s="18" t="n">
-        <v>99332</v>
+        <v>99330.10000000001</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>99332</v>
+        <v>99330.10000000001</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>100423.6</v>
+        <v>100421.7</v>
       </c>
       <c r="Z25" s="18" t="n">
-        <v>100423.6</v>
+        <v>100421.7</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>98240.5</v>
+        <v>98238.60000000001</v>
       </c>
       <c r="AB25" s="18" t="n">
-        <v>99332</v>
+        <v>99330.10000000001</v>
       </c>
       <c r="AC25" s="18" t="n">
-        <v>61397.2</v>
+        <v>61396</v>
       </c>
       <c r="AD25" s="18" t="n">
-        <v>52617.5</v>
+        <v>52616.4</v>
       </c>
       <c r="AE25" s="18" t="n">
-        <v>34572.9</v>
+        <v>34572.2</v>
       </c>
       <c r="AF25" s="18" t="n">
         <v>0</v>
@@ -43770,119 +43770,119 @@
         <v/>
       </c>
       <c r="R31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1348.08)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1346.2)</f>
         <v/>
       </c>
       <c r="S31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="T31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="U31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="V31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="W31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="X31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="Y31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="Z31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AA31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AB31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AC31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AD31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AE31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AF31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AG31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AH31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AI31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AJ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AK31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AL31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AM31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AN31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AO31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AP31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AQ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AR31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AS31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AT31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
     </row>
@@ -56187,7 +56187,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -62088,7 +62088,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1642,121 +1642,121 @@
     <comment ref="AC40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21189억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 321359억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 556억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 21744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 321359억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 556억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 21874억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20382억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 982억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 21365억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 982억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20211억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 21204억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19376억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20380억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18626억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17736억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 18729억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17096억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 18090억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15756억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 16760억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13975억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 14979억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AD41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AF41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AG41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AH41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AI41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AK41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AL41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AM41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AN41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AC42" authorId="0" shapeId="0">
@@ -2317,55 +2317,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 73295억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 73354억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80537억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80674억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 88042억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 88204억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90060억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90207억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98485억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98588억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107481억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107523억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117064억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117035억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121314억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121216억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131967억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131815억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2377,55 +2377,55 @@
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 73295억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 73354억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 80537억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 80674억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 88042억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 88204억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 90060억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 90207억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98485억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98588억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 107481억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 107523억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 117064억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 117035억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 121314억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 121216억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 131967억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 131815억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4194,61 +4194,61 @@
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21189억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 321359억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 556억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 21744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 321359억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 556억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 989억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1006억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 21874억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20382억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 3712억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 982억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 21365억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 982억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20211억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 7800억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 21204억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19376억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 12884억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20380억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18626억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 18598억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17736억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 24573억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 18729억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17096억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 30441억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 993억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 18090억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15756억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 35833억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 16760억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13975억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 3건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 40382억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1004억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 14979억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4264,61 +4264,61 @@
     </comment>
     <comment ref="AC40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
@@ -4869,152 +4869,152 @@
   <commentList>
     <comment ref="E12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
   </commentList>
@@ -5326,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>· 신규수주 — forecast_panel base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 통계 흐름, 공시 계약 개별 반영 아님). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
+          <t>· 신규수주 — forecast_panel base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 공시 계약은 체결 분기별로 패널 신규수주와 상계(SLS 일정 유지)). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 175,212억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −9,541억(2026 1,562억 · 2027 3,984억 · 2028 3,995억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 1,562억 vs 989억 · 2027 3,984억 vs 42,994억 · 2028 3,995억 vs 131,229억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 163,971억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 패널 base 신규 매출 −11,241억(2026 275억 · 2027 4,902억 · 2028 6,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 1,562억 vs 714억 · 2027 3,984억 vs 38,092억 · 2028 3,995억 vs 125,165억 / 총차입금 이자율: 주석 연율 13.9% 가 CF 연율 4.5% 의 3.1배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28511.3</v>
+        <v>28651.3</v>
       </c>
     </row>
     <row r="30">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.49</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="32">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2838</v>
+        <v>0.2852</v>
       </c>
     </row>
     <row r="34">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="35">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>316500</v>
+        <v>318500</v>
       </c>
     </row>
     <row r="36">
@@ -11356,36 +11356,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>0.003553611</v>
+        <v>-0.007408938</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.00380716</v>
+        <v>0.001303595</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.002797985</v>
+        <v>-0.004136055</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5940.248833788</v>
+        <v>5940.241590988</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.002078367</v>
+        <v>0.004678229</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.0010213</v>
+        <v>-0.005786608</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.011516221</v>
+        <v>0.003482107</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>5940.244676766</v>
+        <v>5940.243275892</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.003900756</v>
+        <v>0.007927188</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.002811777</v>
+        <v>0.002003492</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11484,36 +11484,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.000671277</v>
+        <v>-0.010008938</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.005438573</v>
+        <v>0.001303595</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.005511294</v>
+        <v>-0.004136055</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5940.237040959</v>
+        <v>5940.251590988</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.006023743</v>
+        <v>-0.005321771</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.001005347</v>
+        <v>0.004213392</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.009357202</v>
+        <v>0.003482107</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>5940.242381229</v>
+        <v>5940.243275892</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.001500954</v>
+        <v>0.007927188</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.005293033</v>
+        <v>0.002003492</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11740,36 +11740,36 @@
         <v/>
       </c>
       <c r="AC33" s="31" t="n">
-        <v>0.119035577</v>
+        <v>0.120009447</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.106800684</v>
+        <v>0.10785701</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.100002852</v>
+        <v>0.100146758</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.024444944</v>
+        <v>0.024220456</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.099615991</v>
+        <v>0.098934509</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.096737508</v>
+        <v>0.095964125</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.093965857</v>
+        <v>0.09322971100000001</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.03808628</v>
+        <v>0.037483367</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.09197129</v>
+        <v>0.091586822</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.087083779</v>
+        <v>0.086960576</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11868,36 +11868,36 @@
         <v/>
       </c>
       <c r="AC34" s="31" t="n">
-        <v>0.109147918</v>
+        <v>0.110040893</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.09880231</v>
+        <v>0.099785888</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.093186994</v>
+        <v>0.093332819</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.022920881</v>
+        <v>0.022713155</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.093544425</v>
+        <v>0.09291430000000001</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.091345754</v>
+        <v>0.09062110800000001</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.089166944</v>
+        <v>0.088470246</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.036300422</v>
+        <v>0.035725253</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.087809838</v>
+        <v>0.087439514</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.083461541</v>
+        <v>0.083339314</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12573,36 +12573,36 @@
         <v/>
       </c>
       <c r="AC40" s="29" t="n">
-        <v>34829.474339</v>
+        <v>35385.264339</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>34829.478114</v>
+        <v>35835.318114</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>34829.485704</v>
+        <v>35811.865704</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>34829.508695</v>
+        <v>35822.808695</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>34829.431719</v>
+        <v>35833.641719</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>34829.496163</v>
+        <v>35833.706163</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>34829.433631</v>
+        <v>35822.733631</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>34829.42872</v>
+        <v>35822.72872</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>34829.493844</v>
+        <v>35833.713844</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>34829.556985</v>
+        <v>35833.766985</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>매출조선신규 (forecast_panel base 신규수주 매출, 억원 — 가정)</t>
+          <t>매출조선신규 (forecast_panel base · 공시 상계 신규수주 매출, 억원 — 가정)</t>
         </is>
       </c>
       <c r="E41" s="26">
@@ -12722,39 +12722,39 @@
         <v>0</v>
       </c>
       <c r="AD41" s="29" t="n">
-        <v>989.3</v>
+        <v>713.92</v>
       </c>
       <c r="AE41" s="30">
         <f>subQ!AE40</f>
         <v/>
       </c>
       <c r="AF41" s="29" t="n">
-        <v>3711.83</v>
+        <v>2954</v>
       </c>
       <c r="AG41" s="29" t="n">
-        <v>7799.52</v>
+        <v>6661.68</v>
       </c>
       <c r="AH41" s="29" t="n">
-        <v>12884.3</v>
+        <v>11468.92</v>
       </c>
       <c r="AI41" s="29" t="n">
-        <v>18598.11</v>
+        <v>17007.63</v>
       </c>
       <c r="AJ41" s="30">
         <f>subQ!AJ40</f>
         <v/>
       </c>
       <c r="AK41" s="29" t="n">
-        <v>24572.88</v>
+        <v>22909.76</v>
       </c>
       <c r="AL41" s="29" t="n">
-        <v>30440.54</v>
+        <v>28807.24</v>
       </c>
       <c r="AM41" s="29" t="n">
-        <v>35833.03</v>
+        <v>34331.99</v>
       </c>
       <c r="AN41" s="29" t="n">
-        <v>40382.27</v>
+        <v>39115.96</v>
       </c>
       <c r="AO41" s="30">
         <f>subQ!AO40</f>
@@ -12874,42 +12874,42 @@
         <v/>
       </c>
       <c r="AC42" s="31" t="n">
-        <v>0.140604326</v>
+        <v>0.140604211</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.140904368</v>
+        <v>0.140904281</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.140904321</v>
+        <v>0.14090432</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.140932684</v>
+        <v>0.140932691</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.141014867</v>
+        <v>0.141014883</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.141074891</v>
+        <v>0.141074862</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.141134933</v>
+        <v>0.141134868</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.14119495</v>
+        <v>0.141194886</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.141346491</v>
+        <v>0.141346535</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.141567708</v>
+        <v>0.141567651</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2449401802883696</v>
+        <v>0.2449401529793631</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04875938193014453</v>
+        <v>0.04875937702661385</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999997747206621</v>
+        <v>1</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.02472789423886327</v>
+        <v>0.02472805216887641</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.139014154620006</v>
+        <v>0.1390177467320359</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17021,7 +17021,7 @@
         <v>4000</v>
       </c>
       <c r="AB32" s="19" t="n">
-        <v>523403.57</v>
+        <v>3000</v>
       </c>
       <c r="AC32" s="10" t="n"/>
       <c r="AD32" s="10" t="n"/>
@@ -19608,59 +19608,42 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>유동성장기부채</t>
+          <t>사채</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>845229.83</v>
+        <v>536292.3100000001</v>
       </c>
       <c r="F60" s="37" t="n">
-        <v>845229.83</v>
+        <v>536292.3100000001</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>1048626.73</v>
+        <v>844823</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>1514783.97</v>
+        <v>885946</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>1577253.75</v>
+        <v>956970</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>1226167.17</v>
+        <v>873294</v>
       </c>
       <c r="K60" s="37" t="n">
-        <v>1226167.17</v>
+        <v>873294</v>
       </c>
       <c r="L60" s="18" t="n">
-        <v>1143453.19</v>
+        <v>391140</v>
       </c>
       <c r="M60" s="18" t="n">
-        <v>666452.8100000001</v>
+        <v>643175</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>845029.23</v>
+        <v>652871</v>
       </c>
       <c r="P60" s="9" t="n"/>
-      <c r="T60" s="18" t="n">
-        <v>371613.31</v>
-      </c>
-      <c r="U60" s="37" t="n">
-        <v>371613.31</v>
-      </c>
-      <c r="V60" s="18" t="n">
-        <v>386666.87</v>
-      </c>
-      <c r="W60" s="18" t="n">
-        <v>332765.09</v>
-      </c>
-      <c r="X60" s="18" t="n">
-        <v>255898.54</v>
-      </c>
+      <c r="U60" s="9" t="n"/>
       <c r="Z60" s="9" t="n"/>
-      <c r="AA60" s="18" t="n">
-        <v>599939.45</v>
-      </c>
       <c r="AB60" s="5" t="n"/>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -19682,43 +19665,62 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>사채</t>
+          <t>유동성장기부채</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>536292.3100000001</v>
+        <v>845229.83</v>
       </c>
       <c r="F61" s="37" t="n">
-        <v>536292.3100000001</v>
+        <v>845229.83</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>844823</v>
+        <v>1048626.73</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>885946</v>
+        <v>1514783.97</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>956970</v>
+        <v>1577253.75</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>873294</v>
+        <v>1226167.17</v>
       </c>
       <c r="K61" s="37" t="n">
-        <v>873294</v>
+        <v>1226167.17</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>391140</v>
+        <v>1143453.19</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>643175</v>
+        <v>666452.8100000001</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>652871</v>
+        <v>845029.23</v>
       </c>
       <c r="P61" s="9" t="n"/>
-      <c r="U61" s="9" t="n"/>
+      <c r="T61" s="18" t="n">
+        <v>371613.31</v>
+      </c>
+      <c r="U61" s="37" t="n">
+        <v>371613.31</v>
+      </c>
+      <c r="V61" s="18" t="n">
+        <v>386666.87</v>
+      </c>
+      <c r="W61" s="18" t="n">
+        <v>332765.09</v>
+      </c>
+      <c r="X61" s="18" t="n">
+        <v>255898.54</v>
+      </c>
       <c r="Z61" s="9" t="n"/>
-      <c r="AB61" s="5" t="n"/>
+      <c r="AA61" s="18" t="n">
+        <v>599939.45</v>
+      </c>
+      <c r="AB61" s="19" t="n">
+        <v>520403.57</v>
+      </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
       <c r="AE61" s="11" t="n"/>
@@ -19910,9 +19912,7 @@
       <c r="Z64" s="37" t="n">
         <v>156966.8</v>
       </c>
-      <c r="AB64" s="19" t="n">
-        <v>523403.57</v>
-      </c>
+      <c r="AB64" s="5" t="n"/>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
       <c r="AE64" s="11" t="n"/>
@@ -24327,7 +24327,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39108,7 +39108,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>매출 조선·해양(조선·해양플랜트) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(조선·해양플랜트) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E40" s="18" t="n"/>
@@ -54614,7 +54614,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님</t>
+          <t>출처: forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님</t>
         </is>
       </c>
     </row>
@@ -55398,39 +55398,39 @@
         <v>0</v>
       </c>
       <c r="F18" s="34" t="n">
-        <v>712.14</v>
+        <v>436.04</v>
       </c>
       <c r="G18" s="20">
         <f>SUM(E18:F18)</f>
         <v/>
       </c>
       <c r="H18" s="34" t="n">
-        <v>2671.87</v>
+        <v>1912.08</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>5614.2</v>
+        <v>4473.45</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>9274.1</v>
+        <v>7855.15</v>
       </c>
       <c r="K18" s="34" t="n">
-        <v>13386.58</v>
+        <v>11792.16</v>
       </c>
       <c r="L18" s="20">
         <f>SUM(H18:K18)</f>
         <v/>
       </c>
       <c r="M18" s="34" t="n">
-        <v>17686.61</v>
+        <v>16019.47</v>
       </c>
       <c r="N18" s="34" t="n">
-        <v>21909.19</v>
+        <v>20272.08</v>
       </c>
       <c r="O18" s="34" t="n">
-        <v>25789.31</v>
+        <v>24284.98</v>
       </c>
       <c r="P18" s="34" t="n">
-        <v>29061.97</v>
+        <v>27793.15</v>
       </c>
       <c r="Q18" s="20">
         <f>SUM(M18:P18)</f>
@@ -55704,39 +55704,39 @@
         <v>0</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>1524.78</v>
+        <v>1250.25</v>
       </c>
       <c r="G24" s="20">
         <f>SUM(E24:F24)</f>
         <v/>
       </c>
       <c r="H24" s="34" t="n">
-        <v>5721.28</v>
+        <v>4965.7</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>12022.68</v>
+        <v>10888.12</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>19862.2</v>
+        <v>18450.7</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>28673.04</v>
+        <v>27086.66</v>
       </c>
       <c r="L24" s="20">
         <f>SUM(H24:K24)</f>
         <v/>
       </c>
       <c r="M24" s="34" t="n">
-        <v>37888.42</v>
+        <v>36229.2</v>
       </c>
       <c r="N24" s="34" t="n">
-        <v>46941.53</v>
+        <v>45311.53</v>
       </c>
       <c r="O24" s="34" t="n">
-        <v>55265.58</v>
+        <v>53766.84</v>
       </c>
       <c r="P24" s="34" t="n">
-        <v>62293.78</v>
+        <v>61028.36</v>
       </c>
       <c r="Q24" s="20">
         <f>SUM(M24:P24)</f>
@@ -60913,7 +60913,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>매출 조선·해양(조선·해양플랜트) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(조선·해양플랜트) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E40" s="18">
@@ -63706,7 +63706,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>매출 조선·해양(조선·해양플랜트) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(조선·해양플랜트) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E40" s="18">

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21874억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 21872억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21365억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 982억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 21386억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21204억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 21226억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20380억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 20400억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 19650억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18729억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18748억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18090억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18108억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 16760억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 16777억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14979억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14994억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80674억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80671억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 88204억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 88203억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90207억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90209억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98588억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98593억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107523억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107529억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117035억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117043억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121216억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121226억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131815억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131827억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 80674억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 80671억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 88204억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 88203억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 90207억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 90209억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98588억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98593억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 107523억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 107529억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 117035억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 117043억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 121216억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 121226억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 131815억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 131827억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4200,55 +4200,55 @@
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21874억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21872억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21365억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 982억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21386억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21204억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21226억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20380억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 20400억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19650억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18729억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18748억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18090억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 993억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18108억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 16760억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 16777억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14979억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14994억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5541,7 +5541,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 163,971억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 패널 base 신규 매출 −11,241억(2026 275억 · 2027 4,902억 · 2028 6,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 1,562억 vs 714억 · 2027 3,984억 vs 38,092억 · 2028 3,995억 vs 125,165억 / 총차입금 이자율: 주석 연율 13.9% 가 CF 연율 4.5% 의 3.1배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 163,971억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 패널 base 신규 매출 −11,241억(2026 275억 · 2027 4,902억 · 2028 6,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 1,562억 vs 714억 · 2027 3,988억 vs 38,092억 · 2028 3,999억 vs 125,165억 / 총차입금 이자율: 주석 연율 13.9% 가 CF 연율 4.5% 의 3.1배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28651.3</v>
+        <v>28653.2</v>
       </c>
     </row>
     <row r="30">
@@ -7853,7 +7853,7 @@
         <v>131.34</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>11.23</v>
+        <v>8.02</v>
       </c>
       <c r="Z18" s="20" t="n">
         <v>-0</v>
@@ -8556,35 +8556,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8675,35 +8675,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8794,35 +8794,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8913,35 +8913,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9032,35 +9032,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9151,35 +9151,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9270,35 +9270,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9389,35 +9389,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -11356,36 +11356,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.007408938</v>
+        <v>-0.006084223</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.001303595</v>
+        <v>0.006485586</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.004136055</v>
+        <v>-0.002280682</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5940.241590988</v>
+        <v>5940.251441722</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.004678229</v>
+        <v>-0.002952796</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.005786608</v>
+        <v>0.001369966</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.003482107</v>
+        <v>0.012350983</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>5940.243275892</v>
+        <v>5940.25372659</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.007927188</v>
+        <v>0.00414803</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.002003492</v>
+        <v>0.008039416000000001</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11484,36 +11484,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.010008938</v>
+        <v>-0.009504848999999999</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.001303595</v>
+        <v>0.005659847</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.004136055</v>
+        <v>0.006869346</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5940.251590988</v>
+        <v>5940.24054502</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.005321771</v>
+        <v>0.006101095</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.004213392</v>
+        <v>0.000361495</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.003482107</v>
+        <v>0.011277252</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>5940.243275892</v>
+        <v>5940.242584162</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.007927188</v>
+        <v>0.012951705</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.002003492</v>
+        <v>-0.003200485</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11743,33 +11743,33 @@
         <v>0.120009447</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.10785701</v>
+        <v>0.107817815</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.100146758</v>
+        <v>0.100180894</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.024220456</v>
+        <v>0.024248005</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.098934509</v>
+        <v>0.098958247</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.095964125</v>
+        <v>0.095982659</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.09322971100000001</v>
+        <v>0.093243913</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.037483367</v>
+        <v>0.037498251</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.091586822</v>
+        <v>0.091594711</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.086960576</v>
+        <v>0.086965401</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11871,33 +11871,33 @@
         <v>0.110040893</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.099785888</v>
+        <v>0.09974976200000001</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.093332819</v>
+        <v>0.093364272</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.022713155</v>
+        <v>0.022738984</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.09291430000000001</v>
+        <v>0.09293672</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.09062110800000001</v>
+        <v>0.090638833</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.088470246</v>
+        <v>0.08848399899999999</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.035725253</v>
+        <v>0.035739649</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.087439514</v>
+        <v>0.087447306</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.083339314</v>
+        <v>0.083344269</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12576,33 +12576,33 @@
         <v>35385.264339</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>35835.318114</v>
+        <v>35835.219113</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>35811.865704</v>
+        <v>35812.872982</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>35822.808695</v>
+        <v>35823.827443</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>35833.641719</v>
+        <v>35834.673932</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>35833.706163</v>
+        <v>35834.737684</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>35822.733631</v>
+        <v>35823.75471</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>35822.72872</v>
+        <v>35823.746931</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>35833.713844</v>
+        <v>35834.737982</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>35833.766985</v>
+        <v>35834.800437</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12877,39 +12877,39 @@
         <v>0.140604211</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.140904281</v>
+        <v>0.140904283</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.14090432</v>
+        <v>0.140904406</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.140932691</v>
+        <v>0.14093271</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.141014883</v>
+        <v>0.141014829</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.141074862</v>
+        <v>0.141074935</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.141134868</v>
+        <v>0.141134918</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.141194886</v>
+        <v>0.141194976</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.141346535</v>
+        <v>0.141346581</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.141567651</v>
+        <v>0.141567708</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 420,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 400,000원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2449401529793631</v>
+        <v>0.2449400647010494</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04875937702661385</v>
+        <v>0.04875938767847952</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>1</v>
+        <v>0.9999998871490914</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.02472805216887641</v>
+        <v>0.02472802091885307</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.1390177467320359</v>
+        <v>0.1390168718901475</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -42715,91 +42715,91 @@
         <v>1418.75</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Y20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AA20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AC20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AK20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AP20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AQ20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AR20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AS20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AT20" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
     </row>
     <row r="21">
@@ -42853,91 +42853,91 @@
         <v>1439.39</v>
       </c>
       <c r="R21" s="13" t="n">
-        <v>1416.98</v>
+        <v>1416.85</v>
       </c>
       <c r="S21" s="13" t="n">
-        <v>1414.73</v>
+        <v>1416.16</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>1416.51</v>
+        <v>1417.94</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>1421.09</v>
+        <v>1422.52</v>
       </c>
       <c r="V21" s="13" t="n">
-        <v>1422.75</v>
+        <v>1424.18</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>1423.84</v>
+        <v>1425.27</v>
       </c>
       <c r="X21" s="13" t="n">
-        <v>1425.63</v>
+        <v>1427.06</v>
       </c>
       <c r="Y21" s="13" t="n">
-        <v>1425.67</v>
+        <v>1427.1</v>
       </c>
       <c r="Z21" s="13" t="n">
-        <v>1427.55</v>
+        <v>1428.98</v>
       </c>
       <c r="AA21" s="13" t="n">
-        <v>1433.99</v>
+        <v>1435.42</v>
       </c>
       <c r="AB21" s="13" t="n">
-        <v>1431.82</v>
+        <v>1433.26</v>
       </c>
       <c r="AC21" s="13" t="n">
-        <v>1431.63</v>
+        <v>1433.06</v>
       </c>
       <c r="AD21" s="13" t="n">
-        <v>1423.21</v>
+        <v>1424.64</v>
       </c>
       <c r="AE21" s="13" t="n">
-        <v>1419.95</v>
+        <v>1421.38</v>
       </c>
       <c r="AF21" s="13" t="n">
-        <v>1424.14</v>
+        <v>1425.57</v>
       </c>
       <c r="AG21" s="13" t="n">
-        <v>1411.65</v>
+        <v>1413.08</v>
       </c>
       <c r="AH21" s="13" t="n">
-        <v>1396.7</v>
+        <v>1398.13</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1386.24</v>
+        <v>1387.67</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1406.42</v>
+        <v>1407.86</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1416.04</v>
+        <v>1417.47</v>
       </c>
     </row>
     <row r="22">
@@ -42991,91 +42991,91 @@
         <v>2245096.1</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>2280959.9</v>
+        <v>2280737.7</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>2227825.9</v>
+        <v>2230079.3</v>
       </c>
       <c r="T22" s="18" t="n">
-        <v>2212802.8</v>
+        <v>2215038.3</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>2131376.6</v>
+        <v>2133522.8</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>2056386.6</v>
+        <v>2058454.9</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>1965319.2</v>
+        <v>1967294.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>1901334.9</v>
+        <v>1903243.4</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>1769436.3</v>
+        <v>1771212.4</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>1591279.2</v>
+        <v>1592874.3</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>1051714.6</v>
+        <v>1052764.1</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>823845.4</v>
+        <v>824668.8</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>675059.2</v>
+        <v>675733.9</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>427319.5</v>
+        <v>427749.1</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>247299.9</v>
+        <v>247549.2</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>215091.3</v>
+        <v>215307.5</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>92961.3</v>
+        <v>93055.60000000001</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>47385.7</v>
+        <v>47434.3</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>38779.2</v>
+        <v>38819.2</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>17614.1</v>
+        <v>17632</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>14014.7</v>
+        <v>14028.9</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>14014.7</v>
+        <v>14028.9</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>13860.7</v>
+        <v>13874.7</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>14014.7</v>
+        <v>14028.9</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>12474.7</v>
+        <v>12487.3</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>251181.4</v>
@@ -43087,28 +43087,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX22" s="18" t="n">
-        <v>7675912.1</v>
+        <v>7675689.9</v>
       </c>
       <c r="AY22" s="18" t="n">
-        <v>8628391.9</v>
+        <v>8637095.300000001</v>
       </c>
       <c r="AZ22" s="18" t="n">
-        <v>7227369.6</v>
+        <v>7234624.5</v>
       </c>
       <c r="BA22" s="18" t="n">
-        <v>2977938.7</v>
+        <v>2980915.9</v>
       </c>
       <c r="BB22" s="18" t="n">
-        <v>602738.2</v>
+        <v>603346.6</v>
       </c>
       <c r="BC22" s="18" t="n">
-        <v>84730.7</v>
+        <v>84817.39999999999</v>
       </c>
       <c r="BD22" s="18" t="n">
-        <v>56366.8</v>
+        <v>56424</v>
       </c>
       <c r="BE22" s="18" t="n">
-        <v>54518.8</v>
+        <v>54574</v>
       </c>
     </row>
     <row r="23">
@@ -43162,91 +43162,91 @@
         <v>2174443.5</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>2187416.1</v>
+        <v>2187203.1</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>2136461.2</v>
+        <v>2138622.2</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>2120422.9</v>
+        <v>2122564.9</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>2037981.5</v>
+        <v>2040033.3</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>1962991.5</v>
+        <v>1964965.4</v>
       </c>
       <c r="W23" s="18" t="n">
-        <v>1872939.3</v>
+        <v>1874821.1</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>1808955</v>
+        <v>1810770.1</v>
       </c>
       <c r="Y23" s="18" t="n">
-        <v>1676041.3</v>
+        <v>1677722.9</v>
       </c>
       <c r="Z23" s="18" t="n">
-        <v>1497884.1</v>
+        <v>1499384.8</v>
       </c>
       <c r="AA23" s="18" t="n">
-        <v>960349.8</v>
+        <v>961307</v>
       </c>
       <c r="AB23" s="18" t="n">
-        <v>731465.5</v>
+        <v>732195.5</v>
       </c>
       <c r="AC23" s="18" t="n">
-        <v>581664.1</v>
+        <v>582244.4</v>
       </c>
       <c r="AD23" s="18" t="n">
-        <v>333924.4</v>
+        <v>334259.6</v>
       </c>
       <c r="AE23" s="18" t="n">
-        <v>155935.2</v>
+        <v>156092</v>
       </c>
       <c r="AF23" s="18" t="n">
-        <v>122711.4</v>
+        <v>122834.2</v>
       </c>
       <c r="AG23" s="18" t="n">
-        <v>39641</v>
+        <v>39681.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>39641</v>
+        <v>39681.9</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>38779.2</v>
+        <v>38819.2</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>17614.1</v>
+        <v>17632</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>14014.7</v>
+        <v>14028.9</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>14014.7</v>
+        <v>14028.9</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>13860.7</v>
+        <v>13874.7</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>14014.7</v>
+        <v>14028.9</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>12474.7</v>
+        <v>12487.3</v>
       </c>
       <c r="AU23" s="18" t="n">
         <v>251181.4</v>
@@ -43258,28 +43258,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>7484649.4</v>
+        <v>7484436.4</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>8257857.1</v>
+        <v>8266185.8</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>6855819.7</v>
+        <v>6862698.9</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>2607403.8</v>
+        <v>2610006.5</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>357928.6</v>
+        <v>358290</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>84730.7</v>
+        <v>84817.39999999999</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>56366.8</v>
+        <v>56424</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>54518.8</v>
+        <v>54574</v>
       </c>
     </row>
     <row r="24">
@@ -43333,91 +43333,91 @@
         <v>2118864.6</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>2086832.2</v>
+        <v>2086629.1</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>2038222.6</v>
+        <v>2040282.8</v>
       </c>
       <c r="T24" s="18" t="n">
-        <v>2021092.8</v>
+        <v>2023132.9</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>1937559.8</v>
+        <v>1939508.6</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>1862569.8</v>
+        <v>1864440.7</v>
       </c>
       <c r="W24" s="18" t="n">
-        <v>1773609.1</v>
+        <v>1775389</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>1709624.9</v>
+        <v>1711338.1</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>1575619.6</v>
+        <v>1577198.2</v>
       </c>
       <c r="Z24" s="18" t="n">
-        <v>1397462.4</v>
+        <v>1398860.1</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>862111.2</v>
+        <v>862967.6</v>
       </c>
       <c r="AB24" s="18" t="n">
-        <v>632135.4</v>
+        <v>632763.4</v>
       </c>
       <c r="AC24" s="18" t="n">
-        <v>520268.1</v>
+        <v>520785.4</v>
       </c>
       <c r="AD24" s="18" t="n">
-        <v>281307.9</v>
+        <v>281589.2</v>
       </c>
       <c r="AE24" s="18" t="n">
-        <v>121363</v>
+        <v>121484.3</v>
       </c>
       <c r="AF24" s="18" t="n">
-        <v>122711.4</v>
+        <v>122834.2</v>
       </c>
       <c r="AG24" s="18" t="n">
-        <v>39641</v>
+        <v>39681.9</v>
       </c>
       <c r="AH24" s="18" t="n">
-        <v>39641</v>
+        <v>39681.9</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>38779.2</v>
+        <v>38819.2</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>17614.1</v>
+        <v>17632</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>14014.7</v>
+        <v>14028.9</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>14014.7</v>
+        <v>14028.9</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>13860.7</v>
+        <v>13874.7</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>14014.7</v>
+        <v>14028.9</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>14168.7</v>
+        <v>14183.1</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>12474.7</v>
+        <v>12487.3</v>
       </c>
     </row>
     <row r="25">
@@ -43471,46 +43471,46 @@
         <v>55578.9</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>100583.9</v>
+        <v>100573.9</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>98238.60000000001</v>
+        <v>98339.39999999999</v>
       </c>
       <c r="T25" s="18" t="n">
-        <v>99330.10000000001</v>
+        <v>99432</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>100421.7</v>
+        <v>100524.7</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>100421.7</v>
+        <v>100524.7</v>
       </c>
       <c r="W25" s="18" t="n">
-        <v>99330.10000000001</v>
+        <v>99432</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>99330.10000000001</v>
+        <v>99432</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>100421.7</v>
+        <v>100524.7</v>
       </c>
       <c r="Z25" s="18" t="n">
-        <v>100421.7</v>
+        <v>100524.7</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>98238.60000000001</v>
+        <v>98339.39999999999</v>
       </c>
       <c r="AB25" s="18" t="n">
-        <v>99330.10000000001</v>
+        <v>99432</v>
       </c>
       <c r="AC25" s="18" t="n">
-        <v>61396</v>
+        <v>61459</v>
       </c>
       <c r="AD25" s="18" t="n">
-        <v>52616.4</v>
+        <v>52670.4</v>
       </c>
       <c r="AE25" s="18" t="n">
-        <v>34572.2</v>
+        <v>34607.7</v>
       </c>
       <c r="AF25" s="18" t="n">
         <v>0</v>
@@ -43770,119 +43770,119 @@
         <v/>
       </c>
       <c r="R31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1346.2)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1345.74)</f>
         <v/>
       </c>
       <c r="S31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="T31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="U31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="V31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="W31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="X31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="Y31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="Z31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AA31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AB31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AC31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AD31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AE31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AF31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AG31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AH31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AI31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AJ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AK31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AL31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AM31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AN31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AO31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AP31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AQ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AR31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AS31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AT31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21872억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 21869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21386억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 21377억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21226억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 21217억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20400억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 20392억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19650억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 19642억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18748억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18740억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18108억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 16777억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 16770억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14994억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14988억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,7 +2323,7 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80671억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80672억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2335,37 +2335,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90209억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90208억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98593억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98590억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107529억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107526억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117043억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117040억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121226억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121222억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131827억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131822억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,7 +2383,7 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 80671억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 80672억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2395,37 +2395,37 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 90209억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 90208억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98593억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98590억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 107529억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 107526억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 117043억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 117040억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 121226억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 121222억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 131827억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 131822억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4200,55 +4200,55 @@
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21872억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21386억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21377억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21226억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21217억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20400억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 20392억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19650억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19642억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18748억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18740억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18108억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 16777억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 16770억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14994억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14988억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5326,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 43건 중 포함 38건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 8.1 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 미적용 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 43건 중 포함 38건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 8.2 백만원</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 163,971억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 패널 base 신규 매출 −11,241억(2026 275억 · 2027 4,902억 · 2028 6,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 1,562억 vs 714억 · 2027 3,988억 vs 38,092억 · 2028 3,999억 vs 125,165억 / 총차입금 이자율: 주석 연율 13.9% 가 CF 연율 4.5% 의 3.1배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 163,971억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 패널 base 신규 매출 −11,241억(2026 275억 · 2027 4,902억 · 2028 6,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 1,561억 vs 714억 · 2027 3,987억 vs 38,092억 · 2028 3,997억 vs 125,165억 / 총차입금 이자율: 주석 연율 13.9% 가 CF 연율 4.5% 의 3.1배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28653.2</v>
+        <v>28652</v>
       </c>
     </row>
     <row r="30">
@@ -7853,7 +7853,7 @@
         <v>131.34</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>8.02</v>
+        <v>9.35</v>
       </c>
       <c r="Z18" s="20" t="n">
         <v>-0</v>
@@ -8556,35 +8556,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8675,35 +8675,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8794,35 +8794,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8913,35 +8913,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9032,35 +9032,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9151,35 +9151,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9270,35 +9270,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9389,35 +9389,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -11356,36 +11356,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.006084223</v>
+        <v>-0.005934642</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.006485586</v>
+        <v>0.001251888</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.002280682</v>
+        <v>-0.000608067</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5940.251441722</v>
+        <v>5940.253555232</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.002952796</v>
+        <v>0.002408892</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.001369966</v>
+        <v>0.002374049</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.012350983</v>
+        <v>0.006750451</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>5940.25372659</v>
+        <v>5940.24407727</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.00414803</v>
+        <v>0.010963121</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.008039416000000001</v>
+        <v>-0.003579079</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11484,36 +11484,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.009504848999999999</v>
+        <v>-0.010176006</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.005659847</v>
+        <v>-0.000399862</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.006869346</v>
+        <v>-0.002307914</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5940.24054502</v>
+        <v>5940.251761917</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.006101095</v>
+        <v>0.000516748</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.000361495</v>
+        <v>0.010357168</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.011277252</v>
+        <v>-0.005396967</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>5940.242584162</v>
+        <v>5940.251792442</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.012951705</v>
+        <v>-0.001429521</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.003200485</v>
+        <v>0.003941107</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11743,33 +11743,33 @@
         <v>0.120009447</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.107817815</v>
+        <v>0.107828276</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.100180894</v>
+        <v>0.100167312</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.024248005</v>
+        <v>0.024236711</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.098958247</v>
+        <v>0.098948884</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.095982659</v>
+        <v>0.09597536199999999</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.093243913</v>
+        <v>0.093238395</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.037498251</v>
+        <v>0.03749227</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.091594711</v>
+        <v>0.091591714</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.086965401</v>
+        <v>0.086963728</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11871,33 +11871,33 @@
         <v>0.110040893</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.09974976200000001</v>
+        <v>0.099759441</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.093364272</v>
+        <v>0.093351674</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.022738984</v>
+        <v>0.022728388</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.09293672</v>
+        <v>0.09292784799999999</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.090638833</v>
+        <v>0.090631828</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.08848399899999999</v>
+        <v>0.088478631</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.035739649</v>
+        <v>0.035733891</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.087447306</v>
+        <v>0.087444287</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.083344269</v>
+        <v>0.083342519</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12576,33 +12576,33 @@
         <v>35385.264339</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>35835.219113</v>
+        <v>35835.088241</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>35812.872982</v>
+        <v>35812.461863</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>35823.827443</v>
+        <v>35823.403118</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>35834.673932</v>
+        <v>35834.242347</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>35834.737684</v>
+        <v>35834.314247</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>35823.75471</v>
+        <v>35823.335627</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>35823.746931</v>
+        <v>35823.332324</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>35834.737982</v>
+        <v>35834.31751</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>35834.800437</v>
+        <v>35834.372722</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12877,39 +12877,39 @@
         <v>0.140604211</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.140904283</v>
+        <v>0.140904313</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.140904406</v>
+        <v>0.140904353</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.14093271</v>
+        <v>0.140932826</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.141014829</v>
+        <v>0.141014916</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.141074935</v>
+        <v>0.141074931</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.141134918</v>
+        <v>0.141134874</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.141194976</v>
+        <v>0.141194946</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.141346581</v>
+        <v>0.141346592</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.141567708</v>
+        <v>0.141567682</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2449400647010494</v>
+        <v>0.2449401441054458</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04875938767847952</v>
+        <v>0.04875938473247325</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999998871490914</v>
+        <v>0.9999997742827212</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.02472802091885307</v>
+        <v>0.02472788069900983</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.1390168718901475</v>
+        <v>0.1390141761350289</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42715,91 +42715,91 @@
         <v>1418.75</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Y20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AA20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AC20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AK20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AP20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AQ20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AR20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AS20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AT20" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
     </row>
     <row r="21">
@@ -42853,91 +42853,91 @@
         <v>1439.39</v>
       </c>
       <c r="R21" s="13" t="n">
-        <v>1416.85</v>
+        <v>1416.67</v>
       </c>
       <c r="S21" s="13" t="n">
-        <v>1416.16</v>
+        <v>1415.57</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>1417.94</v>
+        <v>1417.35</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>1422.52</v>
+        <v>1421.93</v>
       </c>
       <c r="V21" s="13" t="n">
-        <v>1424.18</v>
+        <v>1423.59</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>1425.27</v>
+        <v>1424.68</v>
       </c>
       <c r="X21" s="13" t="n">
-        <v>1427.06</v>
+        <v>1426.47</v>
       </c>
       <c r="Y21" s="13" t="n">
-        <v>1427.1</v>
+        <v>1426.51</v>
       </c>
       <c r="Z21" s="13" t="n">
-        <v>1428.98</v>
+        <v>1428.39</v>
       </c>
       <c r="AA21" s="13" t="n">
-        <v>1435.42</v>
+        <v>1434.83</v>
       </c>
       <c r="AB21" s="13" t="n">
-        <v>1433.26</v>
+        <v>1432.66</v>
       </c>
       <c r="AC21" s="13" t="n">
-        <v>1433.06</v>
+        <v>1432.47</v>
       </c>
       <c r="AD21" s="13" t="n">
-        <v>1424.64</v>
+        <v>1424.05</v>
       </c>
       <c r="AE21" s="13" t="n">
-        <v>1421.38</v>
+        <v>1420.79</v>
       </c>
       <c r="AF21" s="13" t="n">
-        <v>1425.57</v>
+        <v>1424.98</v>
       </c>
       <c r="AG21" s="13" t="n">
-        <v>1413.08</v>
+        <v>1412.49</v>
       </c>
       <c r="AH21" s="13" t="n">
-        <v>1398.13</v>
+        <v>1397.54</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1387.67</v>
+        <v>1387.08</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1407.86</v>
+        <v>1407.26</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1417.47</v>
+        <v>1416.88</v>
       </c>
     </row>
     <row r="22">
@@ -42991,91 +42991,91 @@
         <v>2245096.1</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>2280737.7</v>
+        <v>2280448</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>2230079.3</v>
+        <v>2229148.7</v>
       </c>
       <c r="T22" s="18" t="n">
-        <v>2215038.3</v>
+        <v>2214115</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>2133522.8</v>
+        <v>2132636.4</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>2058454.9</v>
+        <v>2057600.7</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>1967294.4</v>
+        <v>1966478.6</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>1903243.4</v>
+        <v>1902455.2</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>1771212.4</v>
+        <v>1770478.9</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>1592874.3</v>
+        <v>1592215.5</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>1052764.1</v>
+        <v>1052330.6</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>824668.8</v>
+        <v>824328.8</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>675733.9</v>
+        <v>675455.2</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>427749.1</v>
+        <v>427571.7</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>247549.2</v>
+        <v>247446.2</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>215307.5</v>
+        <v>215218.2</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>93055.60000000001</v>
+        <v>93016.7</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>47434.3</v>
+        <v>47414.2</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>38819.2</v>
+        <v>38802.7</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>17632</v>
+        <v>17624.6</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>14028.9</v>
+        <v>14023</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>14028.9</v>
+        <v>14023</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>13874.7</v>
+        <v>13868.9</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>14028.9</v>
+        <v>14023</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>12487.3</v>
+        <v>12482.1</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>251181.4</v>
@@ -43087,28 +43087,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX22" s="18" t="n">
-        <v>7675689.9</v>
+        <v>7675400.2</v>
       </c>
       <c r="AY22" s="18" t="n">
-        <v>8637095.300000001</v>
+        <v>8633500.800000001</v>
       </c>
       <c r="AZ22" s="18" t="n">
-        <v>7234624.5</v>
+        <v>7231628.2</v>
       </c>
       <c r="BA22" s="18" t="n">
-        <v>2980915.9</v>
+        <v>2979686.3</v>
       </c>
       <c r="BB22" s="18" t="n">
-        <v>603346.6</v>
+        <v>603095.3</v>
       </c>
       <c r="BC22" s="18" t="n">
-        <v>84817.39999999999</v>
+        <v>84781.5</v>
       </c>
       <c r="BD22" s="18" t="n">
-        <v>56424</v>
+        <v>56400.2</v>
       </c>
       <c r="BE22" s="18" t="n">
-        <v>54574</v>
+        <v>54551.1</v>
       </c>
     </row>
     <row r="23">
@@ -43162,91 +43162,91 @@
         <v>2174443.5</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>2187203.1</v>
+        <v>2186925.2</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>2138622.2</v>
+        <v>2137729.7</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>2122564.9</v>
+        <v>2121680.3</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>2040033.3</v>
+        <v>2039185.9</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>1964965.4</v>
+        <v>1964150.2</v>
       </c>
       <c r="W23" s="18" t="n">
-        <v>1874821.1</v>
+        <v>1874043.9</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>1810770.1</v>
+        <v>1810020.5</v>
       </c>
       <c r="Y23" s="18" t="n">
-        <v>1677722.9</v>
+        <v>1677028.4</v>
       </c>
       <c r="Z23" s="18" t="n">
-        <v>1499384.8</v>
+        <v>1498765</v>
       </c>
       <c r="AA23" s="18" t="n">
-        <v>961307</v>
+        <v>960911.7</v>
       </c>
       <c r="AB23" s="18" t="n">
-        <v>732195.5</v>
+        <v>731894</v>
       </c>
       <c r="AC23" s="18" t="n">
-        <v>582244.4</v>
+        <v>582004.7</v>
       </c>
       <c r="AD23" s="18" t="n">
-        <v>334259.6</v>
+        <v>334121.2</v>
       </c>
       <c r="AE23" s="18" t="n">
-        <v>156092</v>
+        <v>156027.3</v>
       </c>
       <c r="AF23" s="18" t="n">
-        <v>122834.2</v>
+        <v>122783.5</v>
       </c>
       <c r="AG23" s="18" t="n">
-        <v>39681.9</v>
+        <v>39665</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>39681.9</v>
+        <v>39665</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>38819.2</v>
+        <v>38802.7</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>17632</v>
+        <v>17624.6</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>14028.9</v>
+        <v>14023</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>14028.9</v>
+        <v>14023</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>13874.7</v>
+        <v>13868.9</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>14028.9</v>
+        <v>14023</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>12487.3</v>
+        <v>12482.1</v>
       </c>
       <c r="AU23" s="18" t="n">
         <v>251181.4</v>
@@ -43258,28 +43258,28 @@
         <v>2596376.9</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>7484436.4</v>
+        <v>7484158.5</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>8266185.8</v>
+        <v>8262746.1</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>6862698.9</v>
+        <v>6859857.8</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>2610006.5</v>
+        <v>2608931.6</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>358290</v>
+        <v>358140.8</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>84817.39999999999</v>
+        <v>84781.5</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>56424</v>
+        <v>56400.2</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>54574</v>
+        <v>54551.1</v>
       </c>
     </row>
     <row r="24">
@@ -43333,91 +43333,91 @@
         <v>2118864.6</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>2086629.1</v>
+        <v>2086364.2</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>2040282.8</v>
+        <v>2039432</v>
       </c>
       <c r="T24" s="18" t="n">
-        <v>2023132.9</v>
+        <v>2022290.3</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>1939508.6</v>
+        <v>1938703.8</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>1864440.7</v>
+        <v>1863668</v>
       </c>
       <c r="W24" s="18" t="n">
-        <v>1775389</v>
+        <v>1774653.9</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>1711338.1</v>
+        <v>1710630.5</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>1577198.2</v>
+        <v>1576546.2</v>
       </c>
       <c r="Z24" s="18" t="n">
-        <v>1398860.1</v>
+        <v>1398282.9</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>862967.6</v>
+        <v>862613.9</v>
       </c>
       <c r="AB24" s="18" t="n">
-        <v>632763.4</v>
+        <v>632504.1</v>
       </c>
       <c r="AC24" s="18" t="n">
-        <v>520785.4</v>
+        <v>520571.8</v>
       </c>
       <c r="AD24" s="18" t="n">
-        <v>281589.2</v>
+        <v>281473</v>
       </c>
       <c r="AE24" s="18" t="n">
-        <v>121484.3</v>
+        <v>121434.2</v>
       </c>
       <c r="AF24" s="18" t="n">
-        <v>122834.2</v>
+        <v>122783.5</v>
       </c>
       <c r="AG24" s="18" t="n">
-        <v>39681.9</v>
+        <v>39665</v>
       </c>
       <c r="AH24" s="18" t="n">
-        <v>39681.9</v>
+        <v>39665</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>38819.2</v>
+        <v>38802.7</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>17632</v>
+        <v>17624.6</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>14028.9</v>
+        <v>14023</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>14028.9</v>
+        <v>14023</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>13874.7</v>
+        <v>13868.9</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>14028.9</v>
+        <v>14023</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>14183.1</v>
+        <v>14177.1</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>12487.3</v>
+        <v>12482.1</v>
       </c>
     </row>
     <row r="25">
@@ -43471,46 +43471,46 @@
         <v>55578.9</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>100573.9</v>
+        <v>100561</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>98339.39999999999</v>
+        <v>98297.8</v>
       </c>
       <c r="T25" s="18" t="n">
-        <v>99432</v>
+        <v>99389.89999999999</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>100524.7</v>
+        <v>100482.1</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>100524.7</v>
+        <v>100482.1</v>
       </c>
       <c r="W25" s="18" t="n">
-        <v>99432</v>
+        <v>99389.89999999999</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>99432</v>
+        <v>99389.89999999999</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>100524.7</v>
+        <v>100482.1</v>
       </c>
       <c r="Z25" s="18" t="n">
-        <v>100524.7</v>
+        <v>100482.1</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>98339.39999999999</v>
+        <v>98297.8</v>
       </c>
       <c r="AB25" s="18" t="n">
-        <v>99432</v>
+        <v>99389.89999999999</v>
       </c>
       <c r="AC25" s="18" t="n">
-        <v>61459</v>
+        <v>61433</v>
       </c>
       <c r="AD25" s="18" t="n">
-        <v>52670.4</v>
+        <v>52648.1</v>
       </c>
       <c r="AE25" s="18" t="n">
-        <v>34607.7</v>
+        <v>34593.1</v>
       </c>
       <c r="AF25" s="18" t="n">
         <v>0</v>
@@ -43770,119 +43770,119 @@
         <v/>
       </c>
       <c r="R31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1345.74)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1345.14)</f>
         <v/>
       </c>
       <c r="S31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="T31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="U31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="V31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="W31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="X31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="Y31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="Z31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AA31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AB31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AC31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AD31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AE31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AF31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AG31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AH31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AI31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AJ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AK31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AL31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AM31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AN31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AO31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AP31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AQ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AR31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AS31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AT31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -5326,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -5326,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.42</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="32">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="33">
@@ -9524,7 +9524,7 @@
         <v>434500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>384500</v>
+        <v>362000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9706,7 +9706,7 @@
         <v>411500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>383000</v>
+        <v>361500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9797,7 +9797,7 @@
         <v>478298.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>412700</v>
+        <v>404250</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -13254,7 +13254,7 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>384500</v>
+        <v>362000</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -56187,7 +56187,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -62088,7 +62088,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -1641,62 +1641,62 @@
     </comment>
     <comment ref="AC40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 321359억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 556억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 21752억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 321340억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 556억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 21869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 286518억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21377억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 21346억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 251696억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 981억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21217억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 21184억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 216874억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20392억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 20356억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 182051억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19642억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 19607억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 147229억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18740억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 18707억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 112407억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 18068억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 77585억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 16770억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 16741억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 42762억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
-        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34829.48; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14988억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+        <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
+SLS 해양 원화 14961억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 7940억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80672억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80676억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 88203억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 88202억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90208억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90203억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98590억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98581억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107526억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107512억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117040억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117021억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121222억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121199억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131822억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131795억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 80672억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 80676억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 88203억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 88202억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 90208억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 90203억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98590억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98581억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 107526억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 107512억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 117040억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 117021억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 121222억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 121199억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 131822억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 131795억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4194,61 +4194,61 @@
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 321359억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 556억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21752억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 321340억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 556억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 286529억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 286518억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21377억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 251700억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21346억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 251696억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 981억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21217억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 216870억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21184억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 216874억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20392억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 182041억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 20356억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 182051억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19642억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 147211억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19607억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 147229억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18740억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 112382억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18707억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 112407억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 77552억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18068억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 77585억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 16770억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 42723억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 16741억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 42762억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14988억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34829억(최근 4분기 '부문매출−SLS' 중위 34829억/분기, 잔여 7893억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14961억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 7940억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5326,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5541,14 +5541,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 163,971억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 패널 base 신규 매출 −11,241억(2026 275억 · 2027 4,902억 · 2028 6,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 1,561억 vs 714억 · 2027 3,987억 vs 38,092억 · 2028 3,997억 vs 125,165억 / 총차입금 이자율: 주석 연율 13.9% 가 CF 연율 4.5% 의 3.1배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 163,971억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 패널 base 신규 매출 −11,241억(2026 275억 · 2027 4,902억 · 2028 6,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 1,561억 vs 714억 · 2027 3,979억 vs 38,092억 · 2028 3,990억 vs 125,165억 / 총차입금 이자율: 주석 연율 13.9% 가 CF 연율 4.5% 의 3.1배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 24.0, "op_wape_pct": 50.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "sls_marine_plus_uncovered_backlog_runoff", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 41613.14, "rev_act": 44178.98, "op_pred": 3826.67, "op_act": 5572.85}, {"q": "2025Q4", "rev_pred": 41613.14, "rev_act": 51930.94, "op_pred": 3826.67, "op_act": 5750.35}, {"q": "2026Q1", "rev_pred": 41460.67, "rev_act": 59163.32, "op_pred": 3812.65, "op_act": 9053.86}, {"q": "2026Q2", "rev_pred": 41536.89, "rev_act": 63321.55, "op_pred": 3819.66, "op_act": 10399.38}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 24.0, "op_wape_pct": 50.3, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "sls_marine_plus_uncovered_backlog_runoff", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 41613.18, "rev_act": 44178.98, "op_pred": 3826.68, "op_act": 5572.85}, {"q": "2025Q4", "rev_pred": 41613.18, "rev_act": 51930.94, "op_pred": 3826.68, "op_act": 5750.35}, {"q": "2026Q1", "rev_pred": 41460.55, "rev_act": 59163.32, "op_pred": 3812.64, "op_act": 9053.86}, {"q": "2026Q2", "rev_pred": 41536.85, "rev_act": 63321.55, "op_pred": 3819.66, "op_act": 10399.38}]}</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28652</v>
+        <v>28647.4</v>
       </c>
     </row>
     <row r="30">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.63</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="32">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="33">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2852</v>
+        <v>0.2851</v>
       </c>
     </row>
     <row r="34">
@@ -7853,7 +7853,7 @@
         <v>131.34</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>9.35</v>
+        <v>14.99</v>
       </c>
       <c r="Z18" s="20" t="n">
         <v>-0</v>
@@ -8556,35 +8556,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8675,35 +8675,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8794,35 +8794,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8913,35 +8913,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9032,35 +9032,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9151,35 +9151,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9270,35 +9270,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9389,35 +9389,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9524,7 +9524,7 @@
         <v>434500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>362000</v>
+        <v>367000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9706,7 +9706,7 @@
         <v>411500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>361500</v>
+        <v>347000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9797,7 +9797,7 @@
         <v>478298.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>404250</v>
+        <v>398642.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11356,36 +11356,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.005934642</v>
+        <v>0.004064344</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.001251888</v>
+        <v>-0.000628815</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.000608067</v>
+        <v>0.000643456</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5940.253555232</v>
+        <v>5940.249463989</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.002408892</v>
+        <v>0.006147354</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.002374049</v>
+        <v>-0.002091269</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.006750451</v>
+        <v>0.014832668</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>5940.24407727</v>
+        <v>5940.24254647</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.010963121</v>
+        <v>0.011168472</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.003579079</v>
+        <v>-0.010055902</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11484,36 +11484,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.010176006</v>
+        <v>0.001464344</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.000399862</v>
+        <v>-0.000628815</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.002307914</v>
+        <v>0.000643456</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5940.251761917</v>
+        <v>5940.249463989</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.000516748</v>
+        <v>0.006147354</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.010357168</v>
+        <v>0.007908731</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.005396967</v>
+        <v>0.004832668</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>5940.251792442</v>
+        <v>5940.25254647</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.001429521</v>
+        <v>0.001168472</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.003941107</v>
+        <v>-5.5902e-05</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11740,36 +11740,36 @@
         <v/>
       </c>
       <c r="AC33" s="31" t="n">
-        <v>0.120009447</v>
+        <v>0.120009282</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.107828276</v>
+        <v>0.107879865</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.100167312</v>
+        <v>0.10010853</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.024236711</v>
+        <v>0.024185136</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.098948884</v>
+        <v>0.098899787</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.09597536199999999</v>
+        <v>0.095936709</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.093238395</v>
+        <v>0.093208365</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.03749227</v>
+        <v>0.037460254</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.091591714</v>
+        <v>0.09157472</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.086963728</v>
+        <v>0.08695264599999999</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11868,36 +11868,36 @@
         <v/>
       </c>
       <c r="AC34" s="31" t="n">
-        <v>0.110040893</v>
+        <v>0.110040742</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.099759441</v>
+        <v>0.099807169</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.093351674</v>
+        <v>0.093297187</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.022728388</v>
+        <v>0.022680013</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.09292784799999999</v>
+        <v>0.09288141499999999</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.090631828</v>
+        <v>0.090594813</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.088478631</v>
+        <v>0.08844951400000001</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.035733891</v>
+        <v>0.0357031</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.087444287</v>
+        <v>0.08742728800000001</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.083342519</v>
+        <v>0.083331165</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12573,36 +12573,36 @@
         <v/>
       </c>
       <c r="AC40" s="29" t="n">
-        <v>35385.264339</v>
+        <v>35378.050384</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>35835.088241</v>
+        <v>35827.551151</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>35812.461863</v>
+        <v>35803.474655</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>35823.403118</v>
+        <v>35814.308529</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>35834.242347</v>
+        <v>35825.210463</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>35834.314247</v>
+        <v>35825.279996</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>35823.335627</v>
+        <v>35814.319639</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>35823.332324</v>
+        <v>35814.311512</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>35834.31751</v>
+        <v>35825.286512</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>35834.372722</v>
+        <v>35825.345512</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12874,42 +12874,42 @@
         <v/>
       </c>
       <c r="AC42" s="31" t="n">
-        <v>0.140604211</v>
+        <v>0.140604336</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.140904313</v>
+        <v>0.140904293</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.140904353</v>
+        <v>0.140904365</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.140932826</v>
+        <v>0.140932754</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.141014916</v>
+        <v>0.141014961</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.141074931</v>
+        <v>0.141074964</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.141134874</v>
+        <v>0.141134955</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.141194946</v>
+        <v>0.141194988</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.141346592</v>
+        <v>0.141346543</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.141567682</v>
+        <v>0.141567596</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -13254,11 +13254,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>362000</v>
+        <v>367000</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 400,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 384,000원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2449401441054458</v>
+        <v>0.2449400698593946</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04875938473247325</v>
+        <v>0.04875938418784499</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999997742827212</v>
+        <v>1</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.02472788069900983</v>
+        <v>0.02472782808229172</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.1390141761350289</v>
+        <v>0.1390142682577942</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40972,52 +40972,52 @@
         </is>
       </c>
       <c r="E5" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>108.252</v>
+        <v>108.778</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>125.717</v>
+        <v>126.244</v>
       </c>
       <c r="I5" s="26" t="n">
-        <v>130.163</v>
+        <v>130.695</v>
       </c>
       <c r="J5" s="26" t="n">
-        <v>152.607</v>
+        <v>153.139</v>
       </c>
       <c r="K5" s="26" t="n">
-        <v>290.665</v>
+        <v>291.185</v>
       </c>
       <c r="L5" s="26" t="n">
-        <v>380.432</v>
+        <v>380.959</v>
       </c>
       <c r="M5" s="26" t="n">
-        <v>535.5700000000001</v>
+        <v>536.102</v>
       </c>
       <c r="N5" s="26" t="n">
-        <v>639.616</v>
+        <v>640.148</v>
       </c>
       <c r="O5" s="26" t="n">
-        <v>886.684</v>
+        <v>887.205</v>
       </c>
       <c r="P5" s="26" t="n">
-        <v>1286.644</v>
+        <v>1287.171</v>
       </c>
       <c r="Q5" s="26" t="n">
-        <v>1559.755</v>
+        <v>1560.288</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>1609.729</v>
+        <v>1610.261</v>
       </c>
       <c r="S5" s="26" t="n">
-        <v>1574.735</v>
+        <v>1575.255</v>
       </c>
       <c r="T5" s="26" t="n">
-        <v>1562.157</v>
+        <v>1562.515</v>
       </c>
       <c r="U5" s="26" t="n">
         <v>1499.817</v>
@@ -41098,19 +41098,19 @@
         <v>8.81</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>190.82</v>
+        <v>191.884</v>
       </c>
       <c r="AV5" s="26" t="n">
-        <v>516.739</v>
+        <v>518.856</v>
       </c>
       <c r="AW5" s="26" t="n">
-        <v>1846.283</v>
+        <v>1848.394</v>
       </c>
       <c r="AX5" s="26" t="n">
-        <v>5342.812</v>
+        <v>5344.925</v>
       </c>
       <c r="AY5" s="26" t="n">
-        <v>6082.072</v>
+        <v>6082.95</v>
       </c>
       <c r="AZ5" s="26" t="n">
         <v>5069.796</v>
@@ -41143,52 +41143,52 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>108.252</v>
+        <v>108.778</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>125.717</v>
+        <v>126.244</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>130.163</v>
+        <v>130.695</v>
       </c>
       <c r="J6" s="26" t="n">
-        <v>152.607</v>
+        <v>153.139</v>
       </c>
       <c r="K6" s="26" t="n">
-        <v>290.665</v>
+        <v>291.185</v>
       </c>
       <c r="L6" s="26" t="n">
-        <v>380.432</v>
+        <v>380.959</v>
       </c>
       <c r="M6" s="26" t="n">
-        <v>535.5700000000001</v>
+        <v>536.102</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>639.616</v>
+        <v>640.148</v>
       </c>
       <c r="O6" s="26" t="n">
-        <v>886.684</v>
+        <v>887.205</v>
       </c>
       <c r="P6" s="26" t="n">
-        <v>1268.621</v>
+        <v>1269.147</v>
       </c>
       <c r="Q6" s="26" t="n">
-        <v>1510.913</v>
+        <v>1511.445</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>1543.739</v>
+        <v>1544.271</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>1510.179</v>
+        <v>1510.7</v>
       </c>
       <c r="T6" s="26" t="n">
-        <v>1496.884</v>
+        <v>1497.243</v>
       </c>
       <c r="U6" s="26" t="n">
         <v>1433.827</v>
@@ -41269,19 +41269,19 @@
         <v>8.81</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>190.82</v>
+        <v>191.884</v>
       </c>
       <c r="AV6" s="26" t="n">
-        <v>516.739</v>
+        <v>518.856</v>
       </c>
       <c r="AW6" s="26" t="n">
-        <v>1846.283</v>
+        <v>1848.394</v>
       </c>
       <c r="AX6" s="26" t="n">
-        <v>5209.957</v>
+        <v>5212.068</v>
       </c>
       <c r="AY6" s="26" t="n">
-        <v>5820.263</v>
+        <v>5821.143</v>
       </c>
       <c r="AZ6" s="26" t="n">
         <v>4807.271</v>
@@ -41314,67 +41314,67 @@
         </is>
       </c>
       <c r="E7" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>94.373</v>
+        <v>94.899</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>94.373</v>
+        <v>94.899</v>
       </c>
       <c r="I7" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="J7" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="K7" s="26" t="n">
-        <v>93.336</v>
+        <v>93.85599999999999</v>
       </c>
       <c r="L7" s="26" t="n">
-        <v>94.373</v>
+        <v>94.899</v>
       </c>
       <c r="M7" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>93.336</v>
+        <v>93.85599999999999</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>94.373</v>
+        <v>94.899</v>
       </c>
       <c r="Q7" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="S7" s="26" t="n">
-        <v>93.336</v>
+        <v>93.85599999999999</v>
       </c>
       <c r="T7" s="26" t="n">
-        <v>64.298</v>
+        <v>64.657</v>
       </c>
       <c r="AU7" s="26" t="n">
-        <v>190.82</v>
+        <v>191.884</v>
       </c>
       <c r="AV7" s="26" t="n">
-        <v>379.566</v>
+        <v>381.682</v>
       </c>
       <c r="AW7" s="26" t="n">
-        <v>378.529</v>
+        <v>380.639</v>
       </c>
       <c r="AX7" s="26" t="n">
-        <v>378.529</v>
+        <v>380.639</v>
       </c>
       <c r="AY7" s="26" t="n">
-        <v>157.634</v>
+        <v>158.513</v>
       </c>
     </row>
     <row r="8">
@@ -42127,52 +42127,52 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>108.252</v>
+        <v>108.778</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>125.717</v>
+        <v>126.244</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>130.163</v>
+        <v>130.695</v>
       </c>
       <c r="J16" s="26" t="n">
-        <v>152.607</v>
+        <v>153.139</v>
       </c>
       <c r="K16" s="26" t="n">
-        <v>290.665</v>
+        <v>291.185</v>
       </c>
       <c r="L16" s="26" t="n">
-        <v>380.432</v>
+        <v>380.959</v>
       </c>
       <c r="M16" s="26" t="n">
-        <v>535.5700000000001</v>
+        <v>536.102</v>
       </c>
       <c r="N16" s="26" t="n">
-        <v>632.655</v>
+        <v>633.187</v>
       </c>
       <c r="O16" s="26" t="n">
-        <v>876.896</v>
+        <v>877.417</v>
       </c>
       <c r="P16" s="26" t="n">
-        <v>1258.724</v>
+        <v>1259.25</v>
       </c>
       <c r="Q16" s="26" t="n">
-        <v>1500.907</v>
+        <v>1501.439</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>1533.733</v>
+        <v>1534.265</v>
       </c>
       <c r="S16" s="26" t="n">
-        <v>1500.391</v>
+        <v>1500.912</v>
       </c>
       <c r="T16" s="26" t="n">
-        <v>1486.987</v>
+        <v>1487.346</v>
       </c>
       <c r="U16" s="26" t="n">
         <v>1423.821</v>
@@ -42223,19 +42223,19 @@
         <v>2.627</v>
       </c>
       <c r="AU16" s="26" t="n">
-        <v>190.82</v>
+        <v>191.884</v>
       </c>
       <c r="AV16" s="26" t="n">
-        <v>516.739</v>
+        <v>518.856</v>
       </c>
       <c r="AW16" s="26" t="n">
-        <v>1839.322</v>
+        <v>1841.433</v>
       </c>
       <c r="AX16" s="26" t="n">
-        <v>5170.26</v>
+        <v>5172.371</v>
       </c>
       <c r="AY16" s="26" t="n">
-        <v>5780.566</v>
+        <v>5781.446</v>
       </c>
       <c r="AZ16" s="26" t="n">
         <v>4767.466</v>
@@ -42544,46 +42544,46 @@
         <v>1315.69</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>1317.54</v>
+        <v>1317.53</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>1325.84</v>
+        <v>1325.79</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>1327.2</v>
+        <v>1327.15</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>1337.36</v>
+        <v>1337.29</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>1391.06</v>
+        <v>1390.93</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>1399.96</v>
+        <v>1399.85</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>1398.81</v>
+        <v>1398.73</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>1404.74</v>
+        <v>1404.67</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>1420.57</v>
+        <v>1420.51</v>
       </c>
       <c r="P19" s="13" t="n">
-        <v>1441.71</v>
+        <v>1441.66</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>1448.24</v>
+        <v>1448.19</v>
       </c>
       <c r="R19" s="13" t="n">
-        <v>1447.32</v>
+        <v>1447.28</v>
       </c>
       <c r="S19" s="13" t="n">
-        <v>1447.32</v>
+        <v>1447.28</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>1449.85</v>
+        <v>1449.82</v>
       </c>
       <c r="U19" s="13" t="n">
         <v>1456.41</v>
@@ -42715,91 +42715,91 @@
         <v>1418.75</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Y20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AA20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AC20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AK20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AP20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AQ20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AR20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AS20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AT20" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
     </row>
     <row r="21">
@@ -42823,121 +42823,121 @@
         <v>1321.32</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>1339.47</v>
+        <v>1339.44</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>1335.9</v>
+        <v>1335.87</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>1355.04</v>
+        <v>1354.99</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>1409.43</v>
+        <v>1409.33</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>1399.53</v>
+        <v>1399.45</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>1395.25</v>
+        <v>1395.2</v>
       </c>
       <c r="N21" s="13" t="n">
-        <v>1418.08</v>
+        <v>1418.02</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>1434.24</v>
+        <v>1434.19</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>1459.72</v>
+        <v>1459.68</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>1439.39</v>
+        <v>1439.36</v>
       </c>
       <c r="R21" s="13" t="n">
-        <v>1416.67</v>
+        <v>1416.18</v>
       </c>
       <c r="S21" s="13" t="n">
-        <v>1415.57</v>
+        <v>1413.02</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>1417.35</v>
+        <v>1414.8</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>1421.93</v>
+        <v>1419.41</v>
       </c>
       <c r="V21" s="13" t="n">
-        <v>1423.59</v>
+        <v>1421.07</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>1424.68</v>
+        <v>1422.16</v>
       </c>
       <c r="X21" s="13" t="n">
-        <v>1426.47</v>
+        <v>1423.95</v>
       </c>
       <c r="Y21" s="13" t="n">
-        <v>1426.51</v>
+        <v>1423.99</v>
       </c>
       <c r="Z21" s="13" t="n">
-        <v>1428.39</v>
+        <v>1425.87</v>
       </c>
       <c r="AA21" s="13" t="n">
-        <v>1434.83</v>
+        <v>1432.31</v>
       </c>
       <c r="AB21" s="13" t="n">
-        <v>1432.66</v>
+        <v>1430.14</v>
       </c>
       <c r="AC21" s="13" t="n">
-        <v>1432.47</v>
+        <v>1429.95</v>
       </c>
       <c r="AD21" s="13" t="n">
-        <v>1424.05</v>
+        <v>1421.53</v>
       </c>
       <c r="AE21" s="13" t="n">
-        <v>1420.79</v>
+        <v>1418.27</v>
       </c>
       <c r="AF21" s="13" t="n">
-        <v>1424.98</v>
+        <v>1422.46</v>
       </c>
       <c r="AG21" s="13" t="n">
-        <v>1412.49</v>
+        <v>1409.97</v>
       </c>
       <c r="AH21" s="13" t="n">
-        <v>1397.54</v>
+        <v>1395.02</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1387.08</v>
+        <v>1384.56</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1407.26</v>
+        <v>1404.74</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1416.88</v>
+        <v>1414.36</v>
       </c>
     </row>
     <row r="22">
@@ -42952,163 +42952,163 @@
         </is>
       </c>
       <c r="E22" s="18" t="n">
-        <v>125470.6</v>
+        <v>126170.6</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>125710.8</v>
+        <v>126412.1</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>143035.6</v>
+        <v>143730.6</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>168394.3</v>
+        <v>169095.8</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>173885.4</v>
+        <v>174592.2</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>206789.1</v>
+        <v>207502.3</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>409670.8</v>
+        <v>410377.2</v>
       </c>
       <c r="L22" s="18" t="n">
-        <v>532426.4</v>
+        <v>533132.2</v>
       </c>
       <c r="M22" s="18" t="n">
-        <v>747256</v>
+        <v>747967.7</v>
       </c>
       <c r="N22" s="18" t="n">
-        <v>907023.7</v>
+        <v>907745.3</v>
       </c>
       <c r="O22" s="18" t="n">
-        <v>1271715.7</v>
+        <v>1272424.3</v>
       </c>
       <c r="P22" s="18" t="n">
-        <v>1878140.4</v>
+        <v>1878862.5</v>
       </c>
       <c r="Q22" s="18" t="n">
-        <v>2245096.1</v>
+        <v>2245812.9</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>2280448</v>
+        <v>2280423.5</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>2229148.7</v>
+        <v>2225868.2</v>
       </c>
       <c r="T22" s="18" t="n">
-        <v>2214115</v>
+        <v>2210652.2</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>2132636.4</v>
+        <v>2128856.9</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>2057600.7</v>
+        <v>2053958.4</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>1966478.6</v>
+        <v>1963000.3</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>1902455.2</v>
+        <v>1899094.3</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>1770478.9</v>
+        <v>1767351.2</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>1592215.5</v>
+        <v>1589406.5</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>1052330.6</v>
+        <v>1050482.4</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>824328.8</v>
+        <v>822878.8</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>675455.2</v>
+        <v>674267</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>427571.7</v>
+        <v>426815</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>247446.2</v>
+        <v>247007.4</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>215218.2</v>
+        <v>214837.6</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>93016.7</v>
+        <v>92850.7</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>47414.2</v>
+        <v>47328.7</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>38802.7</v>
+        <v>38732.2</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>17624.6</v>
+        <v>17593</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>14023</v>
+        <v>13998.1</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>14023</v>
+        <v>13998.1</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>13868.9</v>
+        <v>13844.3</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>14023</v>
+        <v>13998.1</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>12482.1</v>
+        <v>12459.9</v>
       </c>
       <c r="AU22" s="18" t="n">
-        <v>251181.4</v>
+        <v>252582.7</v>
       </c>
       <c r="AV22" s="18" t="n">
-        <v>692104.4</v>
+        <v>694920.9</v>
       </c>
       <c r="AW22" s="18" t="n">
-        <v>2596376.9</v>
+        <v>2599222.4</v>
       </c>
       <c r="AX22" s="18" t="n">
-        <v>7675400.2</v>
+        <v>7677523.2</v>
       </c>
       <c r="AY22" s="18" t="n">
-        <v>8633500.800000001</v>
+        <v>8619335.699999999</v>
       </c>
       <c r="AZ22" s="18" t="n">
-        <v>7231628.2</v>
+        <v>7218852.3</v>
       </c>
       <c r="BA22" s="18" t="n">
-        <v>2979686.3</v>
+        <v>2974443.2</v>
       </c>
       <c r="BB22" s="18" t="n">
-        <v>603095.3</v>
+        <v>602024.4</v>
       </c>
       <c r="BC22" s="18" t="n">
-        <v>84781.5</v>
+        <v>84629</v>
       </c>
       <c r="BD22" s="18" t="n">
-        <v>56400.2</v>
+        <v>56300</v>
       </c>
       <c r="BE22" s="18" t="n">
-        <v>54551.1</v>
+        <v>54454.2</v>
       </c>
     </row>
     <row r="23">
@@ -43123,163 +43123,163 @@
         </is>
       </c>
       <c r="E23" s="18" t="n">
-        <v>125470.6</v>
+        <v>126170.6</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>125710.8</v>
+        <v>126412.1</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>143035.6</v>
+        <v>143730.6</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>168394.3</v>
+        <v>169095.8</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>173885.4</v>
+        <v>174592.2</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>206789.1</v>
+        <v>207502.3</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>409670.8</v>
+        <v>410377.2</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>532426.4</v>
+        <v>533132.2</v>
       </c>
       <c r="M23" s="18" t="n">
-        <v>747256</v>
+        <v>747967.7</v>
       </c>
       <c r="N23" s="18" t="n">
-        <v>907023.7</v>
+        <v>907745.3</v>
       </c>
       <c r="O23" s="18" t="n">
-        <v>1271715.7</v>
+        <v>1272424.3</v>
       </c>
       <c r="P23" s="18" t="n">
-        <v>1851074.1</v>
+        <v>1851796.2</v>
       </c>
       <c r="Q23" s="18" t="n">
-        <v>2174443.5</v>
+        <v>2175160.3</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>2186925.2</v>
+        <v>2186930.7</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>2137729.7</v>
+        <v>2134611.9</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>2121680.3</v>
+        <v>2118382</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>2039185.9</v>
+        <v>2035572.7</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>1964150.2</v>
+        <v>1960674.1</v>
       </c>
       <c r="W23" s="18" t="n">
-        <v>1874043.9</v>
+        <v>1870730</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>1810020.5</v>
+        <v>1806824.1</v>
       </c>
       <c r="Y23" s="18" t="n">
-        <v>1677028.4</v>
+        <v>1674067</v>
       </c>
       <c r="Z23" s="18" t="n">
-        <v>1498765</v>
+        <v>1496122.3</v>
       </c>
       <c r="AA23" s="18" t="n">
-        <v>960911.7</v>
+        <v>959226.1</v>
       </c>
       <c r="AB23" s="18" t="n">
-        <v>731894</v>
+        <v>730608.5</v>
       </c>
       <c r="AC23" s="18" t="n">
-        <v>582004.7</v>
+        <v>580982.8</v>
       </c>
       <c r="AD23" s="18" t="n">
-        <v>334121.2</v>
+        <v>333530.8</v>
       </c>
       <c r="AE23" s="18" t="n">
-        <v>156027.3</v>
+        <v>155751.1</v>
       </c>
       <c r="AF23" s="18" t="n">
-        <v>122783.5</v>
+        <v>122567.4</v>
       </c>
       <c r="AG23" s="18" t="n">
-        <v>39665</v>
+        <v>39592.9</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>39665</v>
+        <v>39592.9</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>38802.7</v>
+        <v>38732.2</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>17624.6</v>
+        <v>17593</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>14023</v>
+        <v>13998.1</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>14023</v>
+        <v>13998.1</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>13868.9</v>
+        <v>13844.3</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>14023</v>
+        <v>13998.1</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>12482.1</v>
+        <v>12459.9</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>251181.4</v>
+        <v>252582.7</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>692104.4</v>
+        <v>694920.9</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>2596376.9</v>
+        <v>2599222.4</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>7484158.5</v>
+        <v>7486311.5</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>8262746.1</v>
+        <v>8249240.7</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>6859857.8</v>
+        <v>6847743.4</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>2608931.6</v>
+        <v>2604348.2</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>358140.8</v>
+        <v>357504.3</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>84781.5</v>
+        <v>84629</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>56400.2</v>
+        <v>56300</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>54551.1</v>
+        <v>54454.2</v>
       </c>
     </row>
     <row r="24">
@@ -43294,130 +43294,130 @@
         </is>
       </c>
       <c r="E24" s="18" t="n">
-        <v>125470.6</v>
+        <v>126170.6</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>125710.8</v>
+        <v>126412.1</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>143035.6</v>
+        <v>143730.6</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>168394.3</v>
+        <v>169095.8</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>173885.4</v>
+        <v>174592.2</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>206789.1</v>
+        <v>207502.3</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>409670.8</v>
+        <v>410377.2</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>532426.4</v>
+        <v>533132.2</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>747256</v>
+        <v>747967.7</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>907023.7</v>
+        <v>907745.3</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>1271715.7</v>
+        <v>1272424.3</v>
       </c>
       <c r="P24" s="18" t="n">
-        <v>1851074.1</v>
+        <v>1851796.2</v>
       </c>
       <c r="Q24" s="18" t="n">
-        <v>2118864.6</v>
+        <v>2119581.4</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>2086364.2</v>
+        <v>2086402.3</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>2039432</v>
+        <v>2036491.6</v>
       </c>
       <c r="T24" s="18" t="n">
-        <v>2022290.3</v>
+        <v>2019171.5</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>1938703.8</v>
+        <v>1935272</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>1863668</v>
+        <v>1860373.4</v>
       </c>
       <c r="W24" s="18" t="n">
-        <v>1774653.9</v>
+        <v>1771519.5</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>1710630.5</v>
+        <v>1707613.6</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>1576546.2</v>
+        <v>1573766.3</v>
       </c>
       <c r="Z24" s="18" t="n">
-        <v>1398282.9</v>
+        <v>1395821.6</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>862613.9</v>
+        <v>861105.9</v>
       </c>
       <c r="AB24" s="18" t="n">
-        <v>632504.1</v>
+        <v>631398.1</v>
       </c>
       <c r="AC24" s="18" t="n">
-        <v>520571.8</v>
+        <v>519660.7</v>
       </c>
       <c r="AD24" s="18" t="n">
-        <v>281473</v>
+        <v>280977.8</v>
       </c>
       <c r="AE24" s="18" t="n">
-        <v>121434.2</v>
+        <v>121220.5</v>
       </c>
       <c r="AF24" s="18" t="n">
-        <v>122783.5</v>
+        <v>122567.4</v>
       </c>
       <c r="AG24" s="18" t="n">
-        <v>39665</v>
+        <v>39592.9</v>
       </c>
       <c r="AH24" s="18" t="n">
-        <v>39665</v>
+        <v>39592.9</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>38802.7</v>
+        <v>38732.2</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>17624.6</v>
+        <v>17593</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>14023</v>
+        <v>13998.1</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>14023</v>
+        <v>13998.1</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>13868.9</v>
+        <v>13844.3</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>14023</v>
+        <v>13998.1</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>14177.1</v>
+        <v>14151.9</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>12482.1</v>
+        <v>12459.9</v>
       </c>
     </row>
     <row r="25">
@@ -43471,46 +43471,46 @@
         <v>55578.9</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>100561</v>
+        <v>100528.4</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>98297.8</v>
+        <v>98120.3</v>
       </c>
       <c r="T25" s="18" t="n">
-        <v>99389.89999999999</v>
+        <v>99210.5</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>100482.1</v>
+        <v>100300.7</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>100482.1</v>
+        <v>100300.7</v>
       </c>
       <c r="W25" s="18" t="n">
-        <v>99389.89999999999</v>
+        <v>99210.5</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>99389.89999999999</v>
+        <v>99210.5</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>100482.1</v>
+        <v>100300.7</v>
       </c>
       <c r="Z25" s="18" t="n">
-        <v>100482.1</v>
+        <v>100300.7</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>98297.8</v>
+        <v>98120.3</v>
       </c>
       <c r="AB25" s="18" t="n">
-        <v>99389.89999999999</v>
+        <v>99210.5</v>
       </c>
       <c r="AC25" s="18" t="n">
-        <v>61433</v>
+        <v>61322.1</v>
       </c>
       <c r="AD25" s="18" t="n">
-        <v>52648.1</v>
+        <v>52553.1</v>
       </c>
       <c r="AE25" s="18" t="n">
-        <v>34593.1</v>
+        <v>34530.6</v>
       </c>
       <c r="AF25" s="18" t="n">
         <v>0</v>
@@ -43770,119 +43770,119 @@
         <v/>
       </c>
       <c r="R31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1345.14)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1343.63)</f>
         <v/>
       </c>
       <c r="S31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="T31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="U31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="V31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="W31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="X31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="Y31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="Z31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AA31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AB31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AC31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AD31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AE31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AF31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AG31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AH31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AI31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AJ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AK31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AL31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AM31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AN31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AO31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AP31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AQ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AR31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AS31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AT31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
     </row>
@@ -47944,7 +47944,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260930800154</t>
+          <t>20261013800234</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -47961,52 +47961,52 @@
         </is>
       </c>
       <c r="E77" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="F77" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="G77" s="26" t="n">
-        <v>94.373</v>
+        <v>94.899</v>
       </c>
       <c r="H77" s="26" t="n">
-        <v>94.373</v>
+        <v>94.899</v>
       </c>
       <c r="I77" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="J77" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="K77" s="26" t="n">
-        <v>93.336</v>
+        <v>93.85599999999999</v>
       </c>
       <c r="L77" s="26" t="n">
-        <v>94.373</v>
+        <v>94.899</v>
       </c>
       <c r="M77" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="N77" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="O77" s="26" t="n">
-        <v>93.336</v>
+        <v>93.85599999999999</v>
       </c>
       <c r="P77" s="26" t="n">
-        <v>94.373</v>
+        <v>94.899</v>
       </c>
       <c r="Q77" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="R77" s="26" t="n">
-        <v>95.41</v>
+        <v>95.94199999999999</v>
       </c>
       <c r="S77" s="26" t="n">
-        <v>93.336</v>
+        <v>93.85599999999999</v>
       </c>
       <c r="T77" s="26" t="n">
-        <v>64.29600000000001</v>
+        <v>64.661</v>
       </c>
       <c r="BG77" s="35" t="n">
         <v>1</v>
@@ -48031,7 +48031,7 @@
         </is>
       </c>
       <c r="BM77" s="26" t="n">
-        <v>1485.076</v>
+        <v>1493.361</v>
       </c>
       <c r="BN77" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>20260930800154</t>
+          <t>20261013800234</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -54402,7 +54402,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>20260930800154</t>
+          <t>20261013800234</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -54414,10 +54414,10 @@
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>1953900</v>
+        <v>1964800</v>
       </c>
       <c r="E170" t="n">
-        <v>1485.076</v>
+        <v>1493.361</v>
       </c>
       <c r="F170" t="n">
         <v>1315.69</v>
@@ -54486,7 +54486,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>⚠ 공시 통화선도 매도 명목액 20760백만$ 을 잔고 대비 환산하면 현물(2026Q2 기말 1550.89원) 기준 0.46(-0.24) · 수주시점 평균환율(1447.56원, 계약 39건) 기준 0.43(-0.27) — 가정 0.70 과 다르다. 약정환율 미공시라 적용하지 않음(참고치 hedge.hedge_ratio_implied_spot·hedge_ratio_implied_sign_rate; 채택은 사용자 결정)</t>
+          <t>⚠ 공시 통화선도 매도 명목액 20760백만$ 을 잔고 대비 환산하면 현물(2026Q2 기말 1550.89원) 기준 0.46(-0.24) · 수주시점 평균환율(1447.51원, 계약 39건) 기준 0.43(-0.27) — 가정 0.70 과 다르다. 약정환율 미공시라 적용하지 않음(참고치 hedge.hedge_ratio_implied_spot·hedge_ratio_implied_sign_rate; 채택은 사용자 결정)</t>
         </is>
       </c>
     </row>
@@ -56187,7 +56187,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -62088,7 +62088,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/329180_model.xlsx
+++ b/argus/kship/models/329180_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 286518억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 21868억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 286518억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21346억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 251696억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 981억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 21384억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 251696억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21184억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 216874억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 21221억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 216874억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20356억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 182051억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 20392억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 182051억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19607억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 147229억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 19641억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 147229억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18707억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 112407억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18740억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 112407억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18068억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 77585억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 77585억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 16741억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 42762억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 16770억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 42762억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 34822.26; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14961억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 7940억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14988억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 7940억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,7 +2323,7 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80676억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 80671억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2335,37 +2335,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90203억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 90206억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98581억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 98588억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107512억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 107523억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117021억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 117036억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121199억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 121217억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131795억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 131817억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,7 +2383,7 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 80676억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 80671억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2395,37 +2395,37 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 90203억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 90206억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 98581억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 98588억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 107512억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 107523억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 117021억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 117036억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 121199억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 121217억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 131795억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 131817억 × 2.47%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 5234억 × 13.90%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4200,55 +4200,55 @@
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 286518억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21868억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 286518억) + 신규수주 매출 714억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21346억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 251696억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 981억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21384억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 251696억) + 신규수주 매출 2954억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 983억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21184억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 216874억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 21221억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 216874억) + 신규수주 매출 6662억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20356억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 182051억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 20392억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 182051억) + 신규수주 매출 11469억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19607억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 147229억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19641억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 147229억) + 신규수주 매출 17008억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18707억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 112407억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18740억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 112407억) + 신규수주 매출 22910억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18068억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 77585억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 992억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 77585억) + 신규수주 매출 28807억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 994억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 16741억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 42762억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 16770억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 42762억) + 신규수주 매출 34332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14961억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 7940억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14988억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 3건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 34822억(최근 4분기 '부문매출−SLS' 중위 34822억/분기, 잔여 7940억) + 신규수주 매출 39116억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억)) · origin 이후 공시 수주 SLS 1005억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5326,7 +5326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 163,971억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 패널 base 신규 매출 −11,241억(2026 275억 · 2027 4,902억 · 2028 6,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 1,561억 vs 714억 · 2027 3,979억 vs 38,092억 · 2028 3,990억 vs 125,165억 / 총차입금 이자율: 주석 연율 13.9% 가 CF 연율 4.5% 의 3.1배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 14.0% 채움에서만, 추정 구간 타겟 10.92%→11.02%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 163,971억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 3건 13,215억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 47,475억 − 공시 13,215억 = 34,260억) — 패널 base 신규 매출 −11,241억(2026 275억 · 2027 4,902억 · 2028 6,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 13,215억 vs 패널 base 신규수주 47,475억(28%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 1,561억 vs 714억 · 2027 3,986억 vs 38,092억 · 2028 3,997억 vs 125,165억 / 총차입금 이자율: 주석 연율 13.9% 가 CF 연율 4.5% 의 3.1배 — 최근 4분기 연속 주석이라 유지(차입금 외 이자 포함 가능 — 주석 확인). 클립 조건: stale 또는 &gt; 20% / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -6595/-4926/-10269/-4298(중위 -5761억) → 추정 2026Q3 +227억(차 +5987억, +104%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28647.4</v>
+        <v>28650.9</v>
       </c>
     </row>
     <row r="30">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.81</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="32">
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="33">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2851</v>
+        <v>0.2852</v>
       </c>
     </row>
     <row r="34">
@@ -7853,7 +7853,7 @@
         <v>131.34</v>
       </c>
       <c r="Y18" s="20" t="n">
-        <v>14.99</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="Z18" s="20" t="n">
         <v>-0</v>
@@ -8556,35 +8556,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8675,35 +8675,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8794,35 +8794,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8913,35 +8913,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9032,35 +9032,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9151,35 +9151,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9270,35 +9270,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9389,35 +9389,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9524,7 +9524,7 @@
         <v>434500</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>367000</v>
+        <v>369000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9797,7 +9797,7 @@
         <v>478298.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>398642.9</v>
+        <v>395062.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11356,36 +11356,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>0.004064344</v>
+        <v>0.001846638</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.000628815</v>
+        <v>-0.003953463</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.000643456</v>
+        <v>0.000615447</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5940.249463989</v>
+        <v>5940.240644472</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.006147354</v>
+        <v>0.009846201000000001</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.002091269</v>
+        <v>-0.003687078</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.014832668</v>
+        <v>0.00723402</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>5940.24254647</v>
+        <v>5940.251009216</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.011168472</v>
+        <v>0.004250544</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.010055902</v>
+        <v>-0.003765865</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11484,36 +11484,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>0.001464344</v>
+        <v>-0.0015741</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.000628815</v>
+        <v>-0.004779296</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.000643456</v>
+        <v>-0.000234528</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5940.249463989</v>
+        <v>5940.249747787</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.006147354</v>
+        <v>-0.001099846</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.007908731</v>
+        <v>0.005304503</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.004832668</v>
+        <v>0.006160329</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>5940.25254647</v>
+        <v>5940.249866814</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.001168472</v>
+        <v>0.003054234</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-5.5902e-05</v>
+        <v>-0.005005766</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11743,33 +11743,33 @@
         <v>0.120009282</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.107879865</v>
+        <v>0.10781562</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.10010853</v>
+        <v>0.100167673</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.024185136</v>
+        <v>0.024233599</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.098899787</v>
+        <v>0.09894085399999999</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.095936709</v>
+        <v>0.095968948</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.093208365</v>
+        <v>0.09323311300000001</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.037460254</v>
+        <v>0.037486219</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.09157472</v>
+        <v>0.091588291</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.08695264599999999</v>
+        <v>0.08696090300000001</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11871,33 +11871,33 @@
         <v>0.110040742</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.099807169</v>
+        <v>0.09974773100000001</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.093297187</v>
+        <v>0.093351937</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.022680013</v>
+        <v>0.022725454</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.09288141499999999</v>
+        <v>0.09292022599999999</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.090594813</v>
+        <v>0.090625663</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.08844951400000001</v>
+        <v>0.088473495</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.0357031</v>
+        <v>0.03572807</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.08742728800000001</v>
+        <v>0.087440869</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.083331165</v>
+        <v>0.08333966800000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12576,33 +12576,33 @@
         <v>35378.050384</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>35827.551151</v>
+        <v>35827.501186</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>35803.474655</v>
+        <v>35805.242859</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>35814.308529</v>
+        <v>35816.093722</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>35825.210463</v>
+        <v>35827.015767</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>35825.279996</v>
+        <v>35827.091132</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>35814.319639</v>
+        <v>35816.104884</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>35814.311512</v>
+        <v>35816.105987</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>35825.286512</v>
+        <v>35827.089886</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>35825.345512</v>
+        <v>35827.149926</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12877,39 +12877,39 @@
         <v>0.140604336</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.140904293</v>
+        <v>0.140904231</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.140904365</v>
+        <v>0.140904384</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.140932754</v>
+        <v>0.140932722</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.141014961</v>
+        <v>0.141014947</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.141074964</v>
+        <v>0.141074947</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.141134955</v>
+        <v>0.141134895</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.141194988</v>
+        <v>0.141194953</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.141346543</v>
+        <v>0.141346596</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.141567596</v>
+        <v>0.141567672</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -13254,11 +13254,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>367000</v>
+        <v>369000</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 384,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 365,500원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2449400698593946</v>
+        <v>0.2449402043715052</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04875938418784499</v>
+        <v>0.04875936834022133</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>1</v>
+        <v>0.9999998871336923</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.02472782808229172</v>
+        <v>0.02472803672282592</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.1390142682577942</v>
+        <v>0.1390178359129366</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24327,7 +24327,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42715,91 +42715,91 @@
         <v>1418.75</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="S20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Y20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AA20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AC20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AK20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AP20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AQ20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AR20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AS20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AT20" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
     </row>
     <row r="21">
@@ -42853,91 +42853,91 @@
         <v>1439.36</v>
       </c>
       <c r="R21" s="13" t="n">
-        <v>1416.18</v>
+        <v>1416.11</v>
       </c>
       <c r="S21" s="13" t="n">
-        <v>1413.02</v>
+        <v>1415.53</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>1414.8</v>
+        <v>1417.31</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>1419.41</v>
+        <v>1421.92</v>
       </c>
       <c r="V21" s="13" t="n">
-        <v>1421.07</v>
+        <v>1423.58</v>
       </c>
       <c r="W21" s="13" t="n">
-        <v>1422.16</v>
+        <v>1424.67</v>
       </c>
       <c r="X21" s="13" t="n">
-        <v>1423.95</v>
+        <v>1426.46</v>
       </c>
       <c r="Y21" s="13" t="n">
-        <v>1423.99</v>
+        <v>1426.5</v>
       </c>
       <c r="Z21" s="13" t="n">
-        <v>1425.87</v>
+        <v>1428.38</v>
       </c>
       <c r="AA21" s="13" t="n">
-        <v>1432.31</v>
+        <v>1434.82</v>
       </c>
       <c r="AB21" s="13" t="n">
-        <v>1430.14</v>
+        <v>1432.65</v>
       </c>
       <c r="AC21" s="13" t="n">
-        <v>1429.95</v>
+        <v>1432.46</v>
       </c>
       <c r="AD21" s="13" t="n">
-        <v>1421.53</v>
+        <v>1424.04</v>
       </c>
       <c r="AE21" s="13" t="n">
-        <v>1418.27</v>
+        <v>1420.78</v>
       </c>
       <c r="AF21" s="13" t="n">
-        <v>1422.46</v>
+        <v>1424.97</v>
       </c>
       <c r="AG21" s="13" t="n">
-        <v>1409.97</v>
+        <v>1412.48</v>
       </c>
       <c r="AH21" s="13" t="n">
-        <v>1395.02</v>
+        <v>1397.53</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1384.56</v>
+        <v>1387.07</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1404.74</v>
+        <v>1407.25</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1414.36</v>
+        <v>1416.87</v>
       </c>
     </row>
     <row r="22">
@@ -42991,91 +42991,91 @@
         <v>2245812.9</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>2280423.5</v>
+        <v>2280307.6</v>
       </c>
       <c r="S22" s="18" t="n">
-        <v>2225868.2</v>
+        <v>2229818.9</v>
       </c>
       <c r="T22" s="18" t="n">
-        <v>2210652.2</v>
+        <v>2214571</v>
       </c>
       <c r="U22" s="18" t="n">
-        <v>2128856.9</v>
+        <v>2132618.4</v>
       </c>
       <c r="V22" s="18" t="n">
-        <v>2053958.4</v>
+        <v>2057583.3</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>1963000.3</v>
+        <v>1966462.1</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>1899094.3</v>
+        <v>1902439.2</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>1767351.2</v>
+        <v>1770464</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>1589406.5</v>
+        <v>1592202.1</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>1050482.4</v>
+        <v>1052321.8</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>822878.8</v>
+        <v>824321.8</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>674267</v>
+        <v>675449.6</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>426815</v>
+        <v>427568.1</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>247007.4</v>
+        <v>247444.2</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>214837.6</v>
+        <v>215216.4</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>92850.7</v>
+        <v>93015.89999999999</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>47328.7</v>
+        <v>47413.8</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>38732.2</v>
+        <v>38802.4</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>17593</v>
+        <v>17624.4</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AL22" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AM22" s="18" t="n">
-        <v>13998.1</v>
+        <v>14022.9</v>
       </c>
       <c r="AN22" s="18" t="n">
-        <v>13998.1</v>
+        <v>14022.9</v>
       </c>
       <c r="AO22" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AP22" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AQ22" s="18" t="n">
-        <v>13844.3</v>
+        <v>13868.8</v>
       </c>
       <c r="AR22" s="18" t="n">
-        <v>13998.1</v>
+        <v>14022.9</v>
       </c>
       <c r="AS22" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AT22" s="18" t="n">
-        <v>12459.9</v>
+        <v>12481.9</v>
       </c>
       <c r="AU22" s="18" t="n">
         <v>252582.7</v>
@@ -43087,28 +43087,28 @@
         <v>2599222.4</v>
       </c>
       <c r="AX22" s="18" t="n">
-        <v>7677523.2</v>
+        <v>7677407.3</v>
       </c>
       <c r="AY22" s="18" t="n">
-        <v>8619335.699999999</v>
+        <v>8634591.6</v>
       </c>
       <c r="AZ22" s="18" t="n">
-        <v>7218852.3</v>
+        <v>7231567.4</v>
       </c>
       <c r="BA22" s="18" t="n">
-        <v>2974443.2</v>
+        <v>2979661.3</v>
       </c>
       <c r="BB22" s="18" t="n">
-        <v>602024.4</v>
+        <v>603090.3</v>
       </c>
       <c r="BC22" s="18" t="n">
-        <v>84629</v>
+        <v>84780.8</v>
       </c>
       <c r="BD22" s="18" t="n">
-        <v>56300</v>
+        <v>56399.8</v>
       </c>
       <c r="BE22" s="18" t="n">
-        <v>54454.2</v>
+        <v>54550.6</v>
       </c>
     </row>
     <row r="23">
@@ -43162,91 +43162,91 @@
         <v>2175160.3</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>2186930.7</v>
+        <v>2186819.5</v>
       </c>
       <c r="S23" s="18" t="n">
-        <v>2134611.9</v>
+        <v>2138400.7</v>
       </c>
       <c r="T23" s="18" t="n">
-        <v>2118382</v>
+        <v>2122137</v>
       </c>
       <c r="U23" s="18" t="n">
-        <v>2035572.7</v>
+        <v>2039168.7</v>
       </c>
       <c r="V23" s="18" t="n">
-        <v>1960674.1</v>
+        <v>1964133.6</v>
       </c>
       <c r="W23" s="18" t="n">
-        <v>1870730</v>
+        <v>1874028.1</v>
       </c>
       <c r="X23" s="18" t="n">
-        <v>1806824.1</v>
+        <v>1810005.2</v>
       </c>
       <c r="Y23" s="18" t="n">
-        <v>1674067</v>
+        <v>1677014.3</v>
       </c>
       <c r="Z23" s="18" t="n">
-        <v>1496122.3</v>
+        <v>1498752.4</v>
       </c>
       <c r="AA23" s="18" t="n">
-        <v>959226.1</v>
+        <v>960903.6</v>
       </c>
       <c r="AB23" s="18" t="n">
-        <v>730608.5</v>
+        <v>731887.9</v>
       </c>
       <c r="AC23" s="18" t="n">
-        <v>580982.8</v>
+        <v>581999.9</v>
       </c>
       <c r="AD23" s="18" t="n">
-        <v>333530.8</v>
+        <v>334118.4</v>
       </c>
       <c r="AE23" s="18" t="n">
-        <v>155751.1</v>
+        <v>156026</v>
       </c>
       <c r="AF23" s="18" t="n">
-        <v>122567.4</v>
+        <v>122782.4</v>
       </c>
       <c r="AG23" s="18" t="n">
-        <v>39592.9</v>
+        <v>39664.6</v>
       </c>
       <c r="AH23" s="18" t="n">
-        <v>39592.9</v>
+        <v>39664.6</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>38732.2</v>
+        <v>38802.4</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>17593</v>
+        <v>17624.4</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>13998.1</v>
+        <v>14022.9</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>13998.1</v>
+        <v>14022.9</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>13844.3</v>
+        <v>13868.8</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>13998.1</v>
+        <v>14022.9</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>12459.9</v>
+        <v>12481.9</v>
       </c>
       <c r="AU23" s="18" t="n">
         <v>252582.7</v>
@@ -43258,28 +43258,28 @@
         <v>2599222.4</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>7486311.5</v>
+        <v>7486200.3</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>8249240.7</v>
+        <v>8263840</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>6847743.4</v>
+        <v>6859800</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>2604348.2</v>
+        <v>2608909.8</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>357504.3</v>
+        <v>358137.6</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>84629</v>
+        <v>84780.8</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>56300</v>
+        <v>56399.8</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>54454.2</v>
+        <v>54550.6</v>
       </c>
     </row>
     <row r="24">
@@ -43333,91 +43333,91 @@
         <v>2119581.4</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>2086402.3</v>
+        <v>2086296.3</v>
       </c>
       <c r="S24" s="18" t="n">
-        <v>2036491.6</v>
+        <v>2040103.8</v>
       </c>
       <c r="T24" s="18" t="n">
-        <v>2019171.5</v>
+        <v>2022747.9</v>
       </c>
       <c r="U24" s="18" t="n">
-        <v>1935272</v>
+        <v>1938687.4</v>
       </c>
       <c r="V24" s="18" t="n">
-        <v>1860373.4</v>
+        <v>1863652.3</v>
       </c>
       <c r="W24" s="18" t="n">
-        <v>1771519.5</v>
+        <v>1774639</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>1707613.6</v>
+        <v>1710616.2</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>1573766.3</v>
+        <v>1576533</v>
       </c>
       <c r="Z24" s="18" t="n">
-        <v>1395821.6</v>
+        <v>1398271.2</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>861105.9</v>
+        <v>862606.7</v>
       </c>
       <c r="AB24" s="18" t="n">
-        <v>631398.1</v>
+        <v>632498.8</v>
       </c>
       <c r="AC24" s="18" t="n">
-        <v>519660.7</v>
+        <v>520567.4</v>
       </c>
       <c r="AD24" s="18" t="n">
-        <v>280977.8</v>
+        <v>281470.7</v>
       </c>
       <c r="AE24" s="18" t="n">
-        <v>121220.5</v>
+        <v>121433.2</v>
       </c>
       <c r="AF24" s="18" t="n">
-        <v>122567.4</v>
+        <v>122782.4</v>
       </c>
       <c r="AG24" s="18" t="n">
-        <v>39592.9</v>
+        <v>39664.6</v>
       </c>
       <c r="AH24" s="18" t="n">
-        <v>39592.9</v>
+        <v>39664.6</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>38732.2</v>
+        <v>38802.4</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>17593</v>
+        <v>17624.4</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>13998.1</v>
+        <v>14022.9</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>13998.1</v>
+        <v>14022.9</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>13844.3</v>
+        <v>13868.8</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>13998.1</v>
+        <v>14022.9</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>14151.9</v>
+        <v>14177</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>12459.9</v>
+        <v>12481.9</v>
       </c>
     </row>
     <row r="25">
@@ -43471,46 +43471,46 @@
         <v>55578.9</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>100528.4</v>
+        <v>100523.2</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>98120.3</v>
+        <v>98296.89999999999</v>
       </c>
       <c r="T25" s="18" t="n">
-        <v>99210.5</v>
+        <v>99389.10000000001</v>
       </c>
       <c r="U25" s="18" t="n">
-        <v>100300.7</v>
+        <v>100481.3</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>100300.7</v>
+        <v>100481.3</v>
       </c>
       <c r="W25" s="18" t="n">
-        <v>99210.5</v>
+        <v>99389.10000000001</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>99210.5</v>
+        <v>99389.10000000001</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>100300.7</v>
+        <v>100481.3</v>
       </c>
       <c r="Z25" s="18" t="n">
-        <v>100300.7</v>
+        <v>100481.3</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>98120.3</v>
+        <v>98296.89999999999</v>
       </c>
       <c r="AB25" s="18" t="n">
-        <v>99210.5</v>
+        <v>99389.10000000001</v>
       </c>
       <c r="AC25" s="18" t="n">
-        <v>61322.1</v>
+        <v>61432.5</v>
       </c>
       <c r="AD25" s="18" t="n">
-        <v>52553.1</v>
+        <v>52647.7</v>
       </c>
       <c r="AE25" s="18" t="n">
-        <v>34530.6</v>
+        <v>34592.8</v>
       </c>
       <c r="AF25" s="18" t="n">
         <v>0</v>
@@ -43770,119 +43770,119 @@
         <v/>
       </c>
       <c r="R31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1343.63)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1343.39)</f>
         <v/>
       </c>
       <c r="S31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="T31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="U31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="V31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="W31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(W$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="X31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="Y31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="Z31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AA31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AB31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AC31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AD31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AE31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AF31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AG31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AH31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AI31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AJ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AK31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AL31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AM31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AN31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AO31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AP31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AQ31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AR31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AS31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AT31" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
     </row>
@@ -56187,7 +56187,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -62088,7 +62088,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
